--- a/xlsx/Copy of World_cup_2026.TomC.xlsx
+++ b/xlsx/Copy of World_cup_2026.TomC.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uio-my.sharepoint.com/personal/stvtc1_uio_no/Documents/Documents/brev/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\haavas\git\VM2026\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="221" documentId="8_{19F31C3E-1BA5-4A61-829B-078653E98123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75EE957A-A5A0-41A5-BF4E-DCEF135C6910}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D57C51BA-F97D-4C97-8DE8-5F134B674A4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T" sheetId="1" state="hidden" r:id="rId1"/>
@@ -22542,13 +22542,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AP157"/>
-  <sheetFormatPr defaultColWidth="14" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="14" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.1796875" bestFit="1" customWidth="1"/>
     <col min="2" max="42" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -22676,7 +22676,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>42</v>
       </c>
@@ -22804,7 +22804,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="3" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>84</v>
       </c>
@@ -22932,7 +22932,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="4" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>125</v>
       </c>
@@ -23060,7 +23060,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>167</v>
       </c>
@@ -23188,7 +23188,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>207</v>
       </c>
@@ -23316,7 +23316,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>245</v>
       </c>
@@ -23444,7 +23444,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>286</v>
       </c>
@@ -23572,7 +23572,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>312</v>
       </c>
@@ -23700,7 +23700,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>341</v>
       </c>
@@ -23828,7 +23828,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>370</v>
       </c>
@@ -23956,7 +23956,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>393</v>
       </c>
@@ -24084,7 +24084,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>342</v>
       </c>
@@ -24212,7 +24212,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>433</v>
       </c>
@@ -24340,7 +24340,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>471</v>
       </c>
@@ -24468,7 +24468,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="18" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>498</v>
       </c>
@@ -24596,7 +24596,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="19" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>527</v>
       </c>
@@ -24724,7 +24724,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="20" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>558</v>
       </c>
@@ -24852,7 +24852,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="21" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>592</v>
       </c>
@@ -24980,7 +24980,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="22" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>626</v>
       </c>
@@ -25108,7 +25108,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="23" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>660</v>
       </c>
@@ -25236,7 +25236,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="24" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>693</v>
       </c>
@@ -25364,7 +25364,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="25" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>725</v>
       </c>
@@ -25492,7 +25492,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="26" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>750</v>
       </c>
@@ -25620,7 +25620,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="27" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>559</v>
       </c>
@@ -25748,7 +25748,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="28" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>794</v>
       </c>
@@ -25876,7 +25876,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="29" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>818</v>
       </c>
@@ -26004,7 +26004,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="30" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>843</v>
       </c>
@@ -26132,7 +26132,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="31" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>871</v>
       </c>
@@ -26260,7 +26260,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="32" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>898</v>
       </c>
@@ -26388,7 +26388,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="33" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>925</v>
       </c>
@@ -26516,7 +26516,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="34" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>949</v>
       </c>
@@ -26644,7 +26644,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="35" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>973</v>
       </c>
@@ -26772,7 +26772,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="36" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>997</v>
       </c>
@@ -26900,7 +26900,7 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="37" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>1024</v>
       </c>
@@ -27028,7 +27028,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="38" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>1058</v>
       </c>
@@ -27156,7 +27156,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="39" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>1077</v>
       </c>
@@ -27284,7 +27284,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="40" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>1093</v>
       </c>
@@ -27412,7 +27412,7 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="41" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>1113</v>
       </c>
@@ -27540,7 +27540,7 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="42" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>1148</v>
       </c>
@@ -27668,7 +27668,7 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="43" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>1180</v>
       </c>
@@ -27796,7 +27796,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="44" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>1198</v>
       </c>
@@ -27924,7 +27924,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="45" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>1237</v>
       </c>
@@ -28052,7 +28052,7 @@
         <v>1263</v>
       </c>
     </row>
-    <row r="46" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>1264</v>
       </c>
@@ -28180,7 +28180,7 @@
         <v>1284</v>
       </c>
     </row>
-    <row r="47" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>1285</v>
       </c>
@@ -28308,7 +28308,7 @@
         <v>1322</v>
       </c>
     </row>
-    <row r="48" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>1323</v>
       </c>
@@ -28436,7 +28436,7 @@
         <v>1348</v>
       </c>
     </row>
-    <row r="49" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>1349</v>
       </c>
@@ -28564,7 +28564,7 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="50" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>1384</v>
       </c>
@@ -28692,7 +28692,7 @@
         <v>1418</v>
       </c>
     </row>
-    <row r="51" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>1419</v>
       </c>
@@ -28820,7 +28820,7 @@
         <v>1448</v>
       </c>
     </row>
-    <row r="52" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>1449</v>
       </c>
@@ -28948,7 +28948,7 @@
         <v>1478</v>
       </c>
     </row>
-    <row r="53" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>1479</v>
       </c>
@@ -29076,7 +29076,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="54" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>1508</v>
       </c>
@@ -29204,7 +29204,7 @@
         <v>1543</v>
       </c>
     </row>
-    <row r="55" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>1544</v>
       </c>
@@ -29332,7 +29332,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="56" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>1565</v>
       </c>
@@ -29460,7 +29460,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="57" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>1604</v>
       </c>
@@ -29588,7 +29588,7 @@
         <v>1632</v>
       </c>
     </row>
-    <row r="58" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>1633</v>
       </c>
@@ -29716,7 +29716,7 @@
         <v>1661</v>
       </c>
     </row>
-    <row r="59" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>1662</v>
       </c>
@@ -29844,7 +29844,7 @@
         <v>1676</v>
       </c>
     </row>
-    <row r="60" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>1677</v>
       </c>
@@ -29972,7 +29972,7 @@
         <v>1696</v>
       </c>
     </row>
-    <row r="61" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>1703</v>
       </c>
@@ -30100,7 +30100,7 @@
         <v>1738</v>
       </c>
     </row>
-    <row r="62" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>1739</v>
       </c>
@@ -30228,7 +30228,7 @@
         <v>1769</v>
       </c>
     </row>
-    <row r="63" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>1770</v>
       </c>
@@ -30356,7 +30356,7 @@
         <v>1797</v>
       </c>
     </row>
-    <row r="64" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>1798</v>
       </c>
@@ -30484,7 +30484,7 @@
         <v>1835</v>
       </c>
     </row>
-    <row r="65" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>1836</v>
       </c>
@@ -30612,7 +30612,7 @@
         <v>1857</v>
       </c>
     </row>
-    <row r="66" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>1858</v>
       </c>
@@ -30740,7 +30740,7 @@
         <v>1882</v>
       </c>
     </row>
-    <row r="67" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>1883</v>
       </c>
@@ -30868,7 +30868,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="68" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>1900</v>
       </c>
@@ -30996,7 +30996,7 @@
         <v>1919</v>
       </c>
     </row>
-    <row r="69" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>1920</v>
       </c>
@@ -31124,7 +31124,7 @@
         <v>1957</v>
       </c>
     </row>
-    <row r="70" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>1958</v>
       </c>
@@ -31252,7 +31252,7 @@
         <v>1994</v>
       </c>
     </row>
-    <row r="71" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>1995</v>
       </c>
@@ -31380,7 +31380,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="72" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>2033</v>
       </c>
@@ -31508,7 +31508,7 @@
         <v>2071</v>
       </c>
     </row>
-    <row r="73" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>2072</v>
       </c>
@@ -31636,7 +31636,7 @@
         <v>2089</v>
       </c>
     </row>
-    <row r="74" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>2090</v>
       </c>
@@ -31764,7 +31764,7 @@
         <v>2125</v>
       </c>
     </row>
-    <row r="75" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>2126</v>
       </c>
@@ -31892,7 +31892,7 @@
         <v>2145</v>
       </c>
     </row>
-    <row r="76" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>2146</v>
       </c>
@@ -32020,7 +32020,7 @@
         <v>2182</v>
       </c>
     </row>
-    <row r="77" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>2183</v>
       </c>
@@ -32148,7 +32148,7 @@
         <v>2183</v>
       </c>
     </row>
-    <row r="78" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>2201</v>
       </c>
@@ -32276,7 +32276,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="79" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>2240</v>
       </c>
@@ -32404,7 +32404,7 @@
         <v>2273</v>
       </c>
     </row>
-    <row r="80" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>2274</v>
       </c>
@@ -32532,7 +32532,7 @@
         <v>2276</v>
       </c>
     </row>
-    <row r="81" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>2304</v>
       </c>
@@ -32660,7 +32660,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="82" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>2340</v>
       </c>
@@ -32788,7 +32788,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="83" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>2375</v>
       </c>
@@ -32916,7 +32916,7 @@
         <v>2391</v>
       </c>
     </row>
-    <row r="84" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>2395</v>
       </c>
@@ -33044,7 +33044,7 @@
         <v>2425</v>
       </c>
     </row>
-    <row r="85" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>2426</v>
       </c>
@@ -33172,7 +33172,7 @@
         <v>2428</v>
       </c>
     </row>
-    <row r="86" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>2458</v>
       </c>
@@ -33300,7 +33300,7 @@
         <v>2492</v>
       </c>
     </row>
-    <row r="87" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>2493</v>
       </c>
@@ -33428,7 +33428,7 @@
         <v>2517</v>
       </c>
     </row>
-    <row r="88" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>2524</v>
       </c>
@@ -33556,7 +33556,7 @@
         <v>2548</v>
       </c>
     </row>
-    <row r="89" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>2549</v>
       </c>
@@ -33684,7 +33684,7 @@
         <v>2569</v>
       </c>
     </row>
-    <row r="90" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>2573</v>
       </c>
@@ -33812,7 +33812,7 @@
         <v>2599</v>
       </c>
     </row>
-    <row r="91" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>2600</v>
       </c>
@@ -33940,7 +33940,7 @@
         <v>2615</v>
       </c>
     </row>
-    <row r="112" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>2616</v>
       </c>
@@ -34068,7 +34068,7 @@
         <v>2621</v>
       </c>
     </row>
-    <row r="113" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>2622</v>
       </c>
@@ -34196,7 +34196,7 @@
         <v>2627</v>
       </c>
     </row>
-    <row r="114" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>2628</v>
       </c>
@@ -34324,7 +34324,7 @@
         <v>2633</v>
       </c>
     </row>
-    <row r="115" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>2634</v>
       </c>
@@ -34452,7 +34452,7 @@
         <v>2639</v>
       </c>
     </row>
-    <row r="116" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>2640</v>
       </c>
@@ -34580,7 +34580,7 @@
         <v>2647</v>
       </c>
     </row>
-    <row r="117" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>2648</v>
       </c>
@@ -34708,7 +34708,7 @@
         <v>2655</v>
       </c>
     </row>
-    <row r="118" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>2656</v>
       </c>
@@ -34836,7 +34836,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="119" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>2663</v>
       </c>
@@ -34964,7 +34964,7 @@
         <v>2669</v>
       </c>
     </row>
-    <row r="120" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>2670</v>
       </c>
@@ -35092,7 +35092,7 @@
         <v>2676</v>
       </c>
     </row>
-    <row r="121" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>2677</v>
       </c>
@@ -35220,7 +35220,7 @@
         <v>2683</v>
       </c>
     </row>
-    <row r="122" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>2684</v>
       </c>
@@ -35348,7 +35348,7 @@
         <v>2690</v>
       </c>
     </row>
-    <row r="123" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>2691</v>
       </c>
@@ -35476,7 +35476,7 @@
         <v>2697</v>
       </c>
     </row>
-    <row r="124" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>2698</v>
       </c>
@@ -35604,7 +35604,7 @@
         <v>2705</v>
       </c>
     </row>
-    <row r="125" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>2706</v>
       </c>
@@ -35732,7 +35732,7 @@
         <v>2713</v>
       </c>
     </row>
-    <row r="126" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>2714</v>
       </c>
@@ -35860,7 +35860,7 @@
         <v>2720</v>
       </c>
     </row>
-    <row r="127" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>2721</v>
       </c>
@@ -35988,7 +35988,7 @@
         <v>2726</v>
       </c>
     </row>
-    <row r="128" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>2727</v>
       </c>
@@ -36116,7 +36116,7 @@
         <v>2746</v>
       </c>
     </row>
-    <row r="129" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>2747</v>
       </c>
@@ -36244,7 +36244,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="130" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>2767</v>
       </c>
@@ -36372,7 +36372,7 @@
         <v>2786</v>
       </c>
     </row>
-    <row r="131" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>2787</v>
       </c>
@@ -36500,7 +36500,7 @@
         <v>2806</v>
       </c>
     </row>
-    <row r="132" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>2807</v>
       </c>
@@ -36628,7 +36628,7 @@
         <v>2826</v>
       </c>
     </row>
-    <row r="133" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>2827</v>
       </c>
@@ -36756,7 +36756,7 @@
         <v>2846</v>
       </c>
     </row>
-    <row r="134" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>2847</v>
       </c>
@@ -36884,7 +36884,7 @@
         <v>2866</v>
       </c>
     </row>
-    <row r="135" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>2867</v>
       </c>
@@ -37012,7 +37012,7 @@
         <v>2886</v>
       </c>
     </row>
-    <row r="136" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>2887</v>
       </c>
@@ -37140,7 +37140,7 @@
         <v>2906</v>
       </c>
     </row>
-    <row r="137" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>2907</v>
       </c>
@@ -37268,7 +37268,7 @@
         <v>2926</v>
       </c>
     </row>
-    <row r="138" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>2927</v>
       </c>
@@ -37396,7 +37396,7 @@
         <v>2946</v>
       </c>
     </row>
-    <row r="139" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>2947</v>
       </c>
@@ -37524,7 +37524,7 @@
         <v>2966</v>
       </c>
     </row>
-    <row r="140" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>2967</v>
       </c>
@@ -37652,7 +37652,7 @@
         <v>2986</v>
       </c>
     </row>
-    <row r="141" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>2987</v>
       </c>
@@ -37780,7 +37780,7 @@
         <v>3006</v>
       </c>
     </row>
-    <row r="142" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>2977</v>
       </c>
@@ -37908,7 +37908,7 @@
         <v>3019</v>
       </c>
     </row>
-    <row r="143" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>2997</v>
       </c>
@@ -38036,7 +38036,7 @@
         <v>3032</v>
       </c>
     </row>
-    <row r="144" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>3033</v>
       </c>
@@ -38164,43 +38164,43 @@
         <v>3073</v>
       </c>
     </row>
-    <row r="145" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A145" s="1"/>
     </row>
-    <row r="146" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A146" s="1"/>
     </row>
-    <row r="147" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A147" s="1"/>
     </row>
-    <row r="148" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A148" s="1"/>
     </row>
-    <row r="149" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A149" s="1"/>
     </row>
-    <row r="150" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A150" s="1"/>
     </row>
-    <row r="151" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A151" s="1"/>
     </row>
-    <row r="152" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A152" s="1"/>
     </row>
-    <row r="153" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A153" s="1"/>
     </row>
-    <row r="154" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A154" s="1"/>
     </row>
-    <row r="155" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A155" s="1"/>
     </row>
-    <row r="156" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A156" s="1"/>
     </row>
-    <row r="157" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>3074</v>
       </c>
@@ -38337,22 +38337,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:AA72"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="1.21875" style="10" customWidth="1"/>
-    <col min="2" max="2" width="18.77734375" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.21875" style="10" customWidth="1"/>
-    <col min="4" max="4" width="9.21875" style="10"/>
-    <col min="5" max="5" width="1.21875" style="10" customWidth="1"/>
-    <col min="6" max="6" width="9.21875" style="10"/>
-    <col min="7" max="7" width="27.5546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="2.77734375" style="10" customWidth="1"/>
-    <col min="9" max="9" width="1.21875" style="10" customWidth="1"/>
-    <col min="10" max="16384" width="9.21875" style="10"/>
+    <col min="1" max="1" width="1.1796875" style="10" customWidth="1"/>
+    <col min="2" max="2" width="18.81640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.1796875" style="10" customWidth="1"/>
+    <col min="4" max="4" width="9.1796875" style="10"/>
+    <col min="5" max="5" width="1.1796875" style="10" customWidth="1"/>
+    <col min="6" max="6" width="9.1796875" style="10"/>
+    <col min="7" max="7" width="27.54296875" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="2.81640625" style="10" customWidth="1"/>
+    <col min="9" max="9" width="1.1796875" style="10" customWidth="1"/>
+    <col min="10" max="16384" width="9.1796875" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:27" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:27" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B2" s="39" t="s">
         <v>3115</v>
       </c>
@@ -38364,7 +38364,7 @@
       <c r="G2" s="40"/>
       <c r="H2" s="41"/>
     </row>
-    <row r="3" spans="2:27" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:27" ht="9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="42"/>
       <c r="C3" s="43"/>
       <c r="D3" s="44"/>
@@ -38372,7 +38372,7 @@
       <c r="G3" s="43"/>
       <c r="H3" s="44"/>
     </row>
-    <row r="4" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B4" s="54" t="s">
         <v>3117</v>
       </c>
@@ -38384,7 +38384,7 @@
       <c r="G4" s="45"/>
       <c r="H4" s="44"/>
     </row>
-    <row r="5" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B5" s="42"/>
       <c r="C5" s="43"/>
       <c r="D5" s="44"/>
@@ -38396,7 +38396,7 @@
       </c>
       <c r="H5" s="44"/>
     </row>
-    <row r="6" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B6" s="54" t="s">
         <v>3120</v>
       </c>
@@ -38412,7 +38412,7 @@
       </c>
       <c r="H6" s="44"/>
     </row>
-    <row r="7" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B7" s="54"/>
       <c r="C7" s="43"/>
       <c r="D7" s="44"/>
@@ -38428,7 +38428,7 @@
         <v>#NAME?</v>
       </c>
     </row>
-    <row r="8" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="54" t="s">
         <v>3126</v>
       </c>
@@ -38444,7 +38444,7 @@
       </c>
       <c r="H8" s="44"/>
     </row>
-    <row r="9" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B9" s="54"/>
       <c r="C9" s="43"/>
       <c r="D9" s="44"/>
@@ -38456,7 +38456,7 @@
       </c>
       <c r="H9" s="44"/>
     </row>
-    <row r="10" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="54" t="s">
         <v>3132</v>
       </c>
@@ -38468,7 +38468,7 @@
       <c r="G10" s="50"/>
       <c r="H10" s="44"/>
     </row>
-    <row r="11" spans="2:27" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:27" ht="9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="54"/>
       <c r="C11" s="43"/>
       <c r="D11" s="44"/>
@@ -38476,7 +38476,7 @@
       <c r="G11" s="52"/>
       <c r="H11" s="53"/>
     </row>
-    <row r="12" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="54" t="s">
         <v>3134</v>
       </c>
@@ -38497,7 +38497,7 @@
       <c r="P12" s="76"/>
       <c r="Q12" s="76"/>
     </row>
-    <row r="13" spans="2:27" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:27" ht="9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="54"/>
       <c r="C13" s="43"/>
       <c r="D13" s="44"/>
@@ -38514,7 +38514,7 @@
       <c r="P13" s="76"/>
       <c r="Q13" s="76"/>
     </row>
-    <row r="14" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="54" t="s">
         <v>3135</v>
       </c>
@@ -38535,7 +38535,7 @@
       <c r="P14" s="76"/>
       <c r="Q14" s="76"/>
     </row>
-    <row r="15" spans="2:27" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:27" ht="9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="51"/>
       <c r="C15" s="52"/>
       <c r="D15" s="53"/>
@@ -38560,7 +38560,7 @@
       <c r="P15" s="76"/>
       <c r="Q15" s="76"/>
     </row>
-    <row r="16" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:27" x14ac:dyDescent="0.35">
       <c r="F16" s="118" t="s">
         <v>3137</v>
       </c>
@@ -38579,7 +38579,7 @@
       <c r="P16" s="76"/>
       <c r="Q16" s="76"/>
     </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B17" s="55"/>
       <c r="C17" s="56"/>
       <c r="D17" s="57"/>
@@ -38598,7 +38598,7 @@
       <c r="P17" s="76"/>
       <c r="Q17" s="76"/>
     </row>
-    <row r="18" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:17" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B18" s="42"/>
       <c r="C18" s="58" t="s">
         <v>3131</v>
@@ -38623,7 +38623,7 @@
       <c r="P18" s="76"/>
       <c r="Q18" s="76"/>
     </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B19" s="59" t="str">
         <f>VLOOKUP("France",T,lang,FALSE)</f>
         <v>France</v>
@@ -38651,7 +38651,7 @@
       <c r="P19" s="76"/>
       <c r="Q19" s="76"/>
     </row>
-    <row r="20" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B20" s="59" t="str">
         <f>VLOOKUP("Spain",T,lang,FALSE)</f>
         <v>Spain</v>
@@ -38679,7 +38679,7 @@
       <c r="P20" s="76"/>
       <c r="Q20" s="76"/>
     </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B21" s="59" t="str">
         <f>VLOOKUP("Argentina",T,lang,FALSE)</f>
         <v>Argentina</v>
@@ -38707,7 +38707,7 @@
       <c r="P21" s="76"/>
       <c r="Q21" s="76"/>
     </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B22" s="59" t="str">
         <f>VLOOKUP("England",T,lang,FALSE)</f>
         <v>England</v>
@@ -38735,7 +38735,7 @@
       <c r="P22" s="76"/>
       <c r="Q22" s="76"/>
     </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B23" s="59" t="str">
         <f>VLOOKUP("Portugal",T,lang,FALSE)</f>
         <v>Portugal</v>
@@ -38763,7 +38763,7 @@
       <c r="P23" s="76"/>
       <c r="Q23" s="76"/>
     </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B24" s="59" t="str">
         <f>VLOOKUP("Brazil",T,lang,FALSE)</f>
         <v>Brazil</v>
@@ -38791,7 +38791,7 @@
       <c r="P24" s="76"/>
       <c r="Q24" s="76"/>
     </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B25" s="59" t="str">
         <f>VLOOKUP("Netherlands",T,lang,FALSE)</f>
         <v>Netherlands</v>
@@ -38819,7 +38819,7 @@
       <c r="P25" s="76"/>
       <c r="Q25" s="76"/>
     </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B26" s="59" t="str">
         <f>VLOOKUP("Morocco",T,lang,FALSE)</f>
         <v>Morocco</v>
@@ -38847,7 +38847,7 @@
       <c r="P26" s="76"/>
       <c r="Q26" s="76"/>
     </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B27" s="59" t="str">
         <f>VLOOKUP("Belgium",T,lang,FALSE)</f>
         <v>Belgium</v>
@@ -38875,7 +38875,7 @@
       <c r="P27" s="76"/>
       <c r="Q27" s="76"/>
     </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B28" s="59" t="str">
         <f>VLOOKUP("Germany",T,lang,FALSE)</f>
         <v>Germany</v>
@@ -38903,7 +38903,7 @@
       <c r="P28" s="76"/>
       <c r="Q28" s="76"/>
     </row>
-    <row r="29" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B29" s="59" t="str">
         <f>VLOOKUP("Croatia",T,lang,FALSE)</f>
         <v>Croatia</v>
@@ -38931,7 +38931,7 @@
       <c r="P29" s="76"/>
       <c r="Q29" s="76"/>
     </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B30" s="59" t="str">
         <f>VLOOKUP("Colombia",T,lang,FALSE)</f>
         <v>Colombia</v>
@@ -38959,7 +38959,7 @@
       <c r="P30" s="76"/>
       <c r="Q30" s="76"/>
     </row>
-    <row r="31" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B31" s="59" t="str">
         <f>VLOOKUP("Senegal",T,lang,FALSE)</f>
         <v>Senegal</v>
@@ -38987,7 +38987,7 @@
       <c r="P31" s="76"/>
       <c r="Q31" s="76"/>
     </row>
-    <row r="32" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B32" s="59" t="str">
         <f>VLOOKUP("Mexico",T,lang,FALSE)</f>
         <v>Mexico</v>
@@ -39015,7 +39015,7 @@
       <c r="P32" s="76"/>
       <c r="Q32" s="76"/>
     </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B33" s="59" t="str">
         <f>VLOOKUP("United States",T,lang,FALSE)</f>
         <v>United States</v>
@@ -39043,7 +39043,7 @@
       <c r="P33" s="76"/>
       <c r="Q33" s="76"/>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B34" s="59" t="str">
         <f>VLOOKUP("Uruguay",T,lang,FALSE)</f>
         <v>Uruguay</v>
@@ -39071,7 +39071,7 @@
       <c r="P34" s="76"/>
       <c r="Q34" s="76"/>
     </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B35" s="59" t="str">
         <f>VLOOKUP("Japan",T,lang,FALSE)</f>
         <v>Japan</v>
@@ -39099,7 +39099,7 @@
       <c r="P35" s="76"/>
       <c r="Q35" s="76"/>
     </row>
-    <row r="36" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B36" s="59" t="str">
         <f>VLOOKUP("Switzerland",T,lang,FALSE)</f>
         <v>Switzerland</v>
@@ -39127,7 +39127,7 @@
       <c r="P36" s="76"/>
       <c r="Q36" s="76"/>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B37" s="59" t="str">
         <f>VLOOKUP("Iran",T,lang,FALSE)</f>
         <v>Iran</v>
@@ -39155,7 +39155,7 @@
       <c r="P37" s="76"/>
       <c r="Q37" s="76"/>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B38" s="59" t="str">
         <f>VLOOKUP("Turkey",T,lang,FALSE)</f>
         <v>Turkey</v>
@@ -39183,7 +39183,7 @@
       <c r="P38" s="76"/>
       <c r="Q38" s="76"/>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B39" s="59" t="str">
         <f>VLOOKUP("Ecuador",T,lang,FALSE)</f>
         <v>Ecuador</v>
@@ -39211,7 +39211,7 @@
       <c r="P39" s="76"/>
       <c r="Q39" s="76"/>
     </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B40" s="59" t="str">
         <f>VLOOKUP("Austria",T,lang,FALSE)</f>
         <v>Austria</v>
@@ -39239,7 +39239,7 @@
       <c r="P40" s="76"/>
       <c r="Q40" s="76"/>
     </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B41" s="59" t="str">
         <f>VLOOKUP("Korea Republic",T,lang,FALSE)</f>
         <v>Korea Republic</v>
@@ -39267,7 +39267,7 @@
       <c r="P41" s="76"/>
       <c r="Q41" s="76"/>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B42" s="59" t="str">
         <f>VLOOKUP("Australia",T,lang,FALSE)</f>
         <v>Australia</v>
@@ -39295,7 +39295,7 @@
       <c r="P42" s="76"/>
       <c r="Q42" s="76"/>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B43" s="59" t="str">
         <f>VLOOKUP("Algeria",T,lang,FALSE)</f>
         <v>Algeria</v>
@@ -39319,7 +39319,7 @@
       <c r="P43" s="76"/>
       <c r="Q43" s="76"/>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B44" s="59" t="str">
         <f>VLOOKUP("Egypt",T,lang,FALSE)</f>
         <v>Egypt</v>
@@ -39347,7 +39347,7 @@
       <c r="P44" s="76"/>
       <c r="Q44" s="76"/>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B45" s="59" t="str">
         <f>VLOOKUP("Canada",T,lang,FALSE)</f>
         <v>Canada</v>
@@ -39375,7 +39375,7 @@
       <c r="P45" s="76"/>
       <c r="Q45" s="76"/>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B46" s="59" t="str">
         <f>VLOOKUP("Norway",T,lang,FALSE)</f>
         <v>Norway</v>
@@ -39403,7 +39403,7 @@
       <c r="P46" s="76"/>
       <c r="Q46" s="76"/>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B47" s="59" t="str">
         <f>VLOOKUP("Panama",T,lang,FALSE)</f>
         <v>Panama</v>
@@ -39431,7 +39431,7 @@
       <c r="P47" s="76"/>
       <c r="Q47" s="76"/>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B48" s="59" t="str">
         <f>VLOOKUP("Ivory Coast",T,lang,FALSE)</f>
         <v>Ivory Coast</v>
@@ -39455,7 +39455,7 @@
       <c r="P48" s="76"/>
       <c r="Q48" s="76"/>
     </row>
-    <row r="49" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B49" s="59" t="str">
         <f>VLOOKUP("Sweden",T,lang,FALSE)</f>
         <v>Sweden</v>
@@ -39479,7 +39479,7 @@
       <c r="P49" s="76"/>
       <c r="Q49" s="76"/>
     </row>
-    <row r="50" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B50" s="59" t="str">
         <f>VLOOKUP("Paraguay",T,lang,FALSE)</f>
         <v>Paraguay</v>
@@ -39503,7 +39503,7 @@
       <c r="P50" s="76"/>
       <c r="Q50" s="76"/>
     </row>
-    <row r="51" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B51" s="59" t="str">
         <f>VLOOKUP("Czech Republic",T,lang,FALSE)</f>
         <v>Czech Republic</v>
@@ -39527,7 +39527,7 @@
       <c r="P51" s="76"/>
       <c r="Q51" s="76"/>
     </row>
-    <row r="52" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B52" s="59" t="str">
         <f>VLOOKUP("Scotland",T,lang,FALSE)</f>
         <v>Scotland</v>
@@ -39551,7 +39551,7 @@
       <c r="P52" s="76"/>
       <c r="Q52" s="76"/>
     </row>
-    <row r="53" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B53" s="59" t="str">
         <f>VLOOKUP("Tunisia",T,lang,FALSE)</f>
         <v>Tunisia</v>
@@ -39575,7 +39575,7 @@
       <c r="P53" s="76"/>
       <c r="Q53" s="76"/>
     </row>
-    <row r="54" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B54" s="59" t="str">
         <f>VLOOKUP("DR Congo",T,lang,FALSE)</f>
         <v>DR Congo</v>
@@ -39599,7 +39599,7 @@
       <c r="P54" s="76"/>
       <c r="Q54" s="76"/>
     </row>
-    <row r="55" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B55" s="59" t="str">
         <f>VLOOKUP("Uzbekistan",T,lang,FALSE)</f>
         <v>Uzbekistan</v>
@@ -39623,7 +39623,7 @@
       <c r="P55" s="76"/>
       <c r="Q55" s="76"/>
     </row>
-    <row r="56" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B56" s="59" t="str">
         <f>VLOOKUP("Qatar",T,lang,FALSE)</f>
         <v>Qatar</v>
@@ -39647,7 +39647,7 @@
       <c r="P56" s="76"/>
       <c r="Q56" s="76"/>
     </row>
-    <row r="57" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B57" s="59" t="str">
         <f>VLOOKUP("Iraq",T,lang,FALSE)</f>
         <v>Iraq</v>
@@ -39671,7 +39671,7 @@
       <c r="P57" s="76"/>
       <c r="Q57" s="76"/>
     </row>
-    <row r="58" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B58" s="59" t="str">
         <f>VLOOKUP("South Africa",T,lang,FALSE)</f>
         <v>South Africa</v>
@@ -39695,7 +39695,7 @@
       <c r="P58" s="76"/>
       <c r="Q58" s="76"/>
     </row>
-    <row r="59" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B59" s="59" t="str">
         <f>VLOOKUP("Saudi Arabia",T,lang,FALSE)</f>
         <v>Saudi Arabia</v>
@@ -39719,7 +39719,7 @@
       <c r="P59" s="76"/>
       <c r="Q59" s="76"/>
     </row>
-    <row r="60" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B60" s="59" t="str">
         <f>VLOOKUP("Jordan",T,lang,FALSE)</f>
         <v>Jordan</v>
@@ -39743,7 +39743,7 @@
       <c r="P60" s="76"/>
       <c r="Q60" s="76"/>
     </row>
-    <row r="61" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B61" s="59" t="str">
         <f>VLOOKUP("Bosnia and Herzegovina",T,lang,FALSE)</f>
         <v>Bosnia and Herzegovina</v>
@@ -39767,7 +39767,7 @@
       <c r="P61" s="76"/>
       <c r="Q61" s="76"/>
     </row>
-    <row r="62" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B62" s="59" t="str">
         <f>VLOOKUP("Cape Verde",T,lang,FALSE)</f>
         <v>Cape Verde</v>
@@ -39791,7 +39791,7 @@
       <c r="P62" s="76"/>
       <c r="Q62" s="76"/>
     </row>
-    <row r="63" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B63" s="59" t="str">
         <f>VLOOKUP("Ghana",T,lang,FALSE)</f>
         <v>Ghana</v>
@@ -39815,7 +39815,7 @@
       <c r="P63" s="76"/>
       <c r="Q63" s="76"/>
     </row>
-    <row r="64" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B64" s="59" t="str">
         <f>VLOOKUP("Curaçao",T,lang,FALSE)</f>
         <v>Curaçao</v>
@@ -39839,7 +39839,7 @@
       <c r="P64" s="76"/>
       <c r="Q64" s="76"/>
     </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B65" s="59" t="str">
         <f>VLOOKUP("Haiti",T,lang,FALSE)</f>
         <v>Haiti</v>
@@ -39866,7 +39866,7 @@
       <c r="P65" s="76"/>
       <c r="Q65" s="76"/>
     </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B66" s="59" t="str">
         <f>VLOOKUP("New Zealand",T,lang,FALSE)</f>
         <v>New Zealand</v>
@@ -39888,7 +39888,7 @@
       <c r="P66" s="76"/>
       <c r="Q66" s="76"/>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B67" s="51"/>
       <c r="C67" s="52"/>
       <c r="D67" s="53"/>
@@ -39905,7 +39905,7 @@
       <c r="P67" s="76"/>
       <c r="Q67" s="76"/>
     </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:17" x14ac:dyDescent="0.35">
       <c r="F68" s="76"/>
       <c r="G68" s="76"/>
       <c r="H68" s="76"/>
@@ -39919,7 +39919,7 @@
       <c r="P68" s="76"/>
       <c r="Q68" s="76"/>
     </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:17" x14ac:dyDescent="0.35">
       <c r="F69" s="76"/>
       <c r="G69" s="76"/>
       <c r="H69" s="76"/>
@@ -39933,7 +39933,7 @@
       <c r="P69" s="76"/>
       <c r="Q69" s="76"/>
     </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:17" x14ac:dyDescent="0.35">
       <c r="F70" s="76"/>
       <c r="G70" s="76"/>
       <c r="H70" s="76"/>
@@ -39947,7 +39947,7 @@
       <c r="P70" s="76"/>
       <c r="Q70" s="76"/>
     </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:17" x14ac:dyDescent="0.35">
       <c r="F71" s="76"/>
       <c r="G71" s="76"/>
       <c r="H71" s="76"/>
@@ -39961,7 +39961,7 @@
       <c r="P71" s="76"/>
       <c r="Q71" s="76"/>
     </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:17" x14ac:dyDescent="0.35">
       <c r="F72" s="76"/>
       <c r="G72" s="76"/>
       <c r="H72" s="76"/>
@@ -40011,62 +40011,62 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:CR111"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="4.77734375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="6.21875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="11.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.81640625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="6.1796875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="4" customWidth="1"/>
-    <col min="5" max="5" width="22.5546875" style="5" customWidth="1"/>
-    <col min="6" max="7" width="4.21875" style="6" customWidth="1"/>
-    <col min="8" max="8" width="22.5546875" style="7" customWidth="1"/>
-    <col min="9" max="9" width="3.44140625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="19.44140625" style="8" customWidth="1"/>
-    <col min="11" max="14" width="5.44140625" style="9" customWidth="1"/>
-    <col min="15" max="15" width="7.77734375" style="9" customWidth="1"/>
-    <col min="16" max="16" width="6.77734375" style="9" customWidth="1"/>
-    <col min="17" max="17" width="3.44140625" style="68" customWidth="1"/>
-    <col min="18" max="18" width="15.44140625" style="123" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="22.54296875" style="5" customWidth="1"/>
+    <col min="6" max="7" width="4.1796875" style="6" customWidth="1"/>
+    <col min="8" max="8" width="22.54296875" style="7" customWidth="1"/>
+    <col min="9" max="9" width="3.453125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="19.453125" style="8" customWidth="1"/>
+    <col min="11" max="14" width="5.453125" style="9" customWidth="1"/>
+    <col min="15" max="15" width="7.81640625" style="9" customWidth="1"/>
+    <col min="16" max="16" width="6.81640625" style="9" customWidth="1"/>
+    <col min="17" max="17" width="3.453125" style="68" customWidth="1"/>
+    <col min="18" max="18" width="15.453125" style="123" hidden="1" customWidth="1"/>
     <col min="19" max="20" width="16" style="127" hidden="1" customWidth="1"/>
     <col min="21" max="28" width="4" style="123" hidden="1" customWidth="1"/>
-    <col min="29" max="29" width="4.21875" style="124" hidden="1" customWidth="1"/>
-    <col min="30" max="30" width="5.44140625" style="123" hidden="1" customWidth="1"/>
-    <col min="31" max="31" width="13.44140625" style="124" hidden="1" customWidth="1"/>
-    <col min="32" max="36" width="5.44140625" style="123" hidden="1" customWidth="1"/>
+    <col min="29" max="29" width="4.1796875" style="124" hidden="1" customWidth="1"/>
+    <col min="30" max="30" width="5.453125" style="123" hidden="1" customWidth="1"/>
+    <col min="31" max="31" width="13.453125" style="124" hidden="1" customWidth="1"/>
+    <col min="32" max="36" width="5.453125" style="123" hidden="1" customWidth="1"/>
     <col min="37" max="39" width="6" style="123" hidden="1" customWidth="1"/>
-    <col min="40" max="40" width="5.44140625" style="123" hidden="1" customWidth="1"/>
+    <col min="40" max="40" width="5.453125" style="123" hidden="1" customWidth="1"/>
     <col min="41" max="42" width="6" style="123" hidden="1" customWidth="1"/>
-    <col min="43" max="43" width="7.21875" style="125" hidden="1" customWidth="1"/>
+    <col min="43" max="43" width="7.1796875" style="125" hidden="1" customWidth="1"/>
     <col min="44" max="44" width="10" style="125" hidden="1" customWidth="1"/>
-    <col min="45" max="45" width="15.21875" style="125" hidden="1" customWidth="1"/>
-    <col min="46" max="50" width="4.77734375" style="126" hidden="1" customWidth="1"/>
-    <col min="51" max="51" width="9.21875" style="125" hidden="1" customWidth="1"/>
-    <col min="52" max="61" width="9.21875" style="126" hidden="1" customWidth="1"/>
-    <col min="62" max="62" width="9.21875" style="112" hidden="1" customWidth="1"/>
-    <col min="63" max="63" width="3.21875" style="2" customWidth="1"/>
-    <col min="64" max="64" width="19.77734375" style="2" customWidth="1"/>
+    <col min="45" max="45" width="15.1796875" style="125" hidden="1" customWidth="1"/>
+    <col min="46" max="50" width="4.81640625" style="126" hidden="1" customWidth="1"/>
+    <col min="51" max="51" width="9.1796875" style="125" hidden="1" customWidth="1"/>
+    <col min="52" max="61" width="9.1796875" style="126" hidden="1" customWidth="1"/>
+    <col min="62" max="62" width="9.1796875" style="112" hidden="1" customWidth="1"/>
+    <col min="63" max="63" width="3.1796875" style="2" customWidth="1"/>
+    <col min="64" max="64" width="19.81640625" style="2" customWidth="1"/>
     <col min="65" max="67" width="3" style="2" customWidth="1"/>
     <col min="68" max="69" width="2" style="111" customWidth="1"/>
-    <col min="70" max="70" width="3.21875" style="2" customWidth="1"/>
-    <col min="71" max="71" width="19.77734375" style="2" customWidth="1"/>
+    <col min="70" max="70" width="3.1796875" style="2" customWidth="1"/>
+    <col min="71" max="71" width="19.81640625" style="2" customWidth="1"/>
     <col min="72" max="74" width="3" style="2" customWidth="1"/>
     <col min="75" max="76" width="2" style="111" customWidth="1"/>
     <col min="77" max="77" width="4" style="2" customWidth="1"/>
-    <col min="78" max="78" width="19.77734375" style="2" customWidth="1"/>
+    <col min="78" max="78" width="19.81640625" style="2" customWidth="1"/>
     <col min="79" max="81" width="3" style="2" customWidth="1"/>
     <col min="82" max="83" width="2" style="111" customWidth="1"/>
-    <col min="84" max="84" width="3.77734375" style="2" customWidth="1"/>
-    <col min="85" max="85" width="19.77734375" style="2" customWidth="1"/>
+    <col min="84" max="84" width="3.81640625" style="2" customWidth="1"/>
+    <col min="85" max="85" width="19.81640625" style="2" customWidth="1"/>
     <col min="86" max="88" width="3" style="2" customWidth="1"/>
     <col min="89" max="90" width="2" style="111" customWidth="1"/>
-    <col min="91" max="91" width="3.77734375" style="2" customWidth="1"/>
-    <col min="92" max="92" width="19.77734375" style="2" customWidth="1"/>
+    <col min="91" max="91" width="3.81640625" style="2" customWidth="1"/>
+    <col min="92" max="92" width="19.81640625" style="2" customWidth="1"/>
     <col min="93" max="95" width="3" style="2" customWidth="1"/>
     <col min="96" max="96" width="2" style="111" customWidth="1"/>
-    <col min="97" max="16384" width="9.21875" style="2"/>
+    <col min="97" max="16384" width="9.1796875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:95" ht="46.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:95" ht="46" x14ac:dyDescent="0.35">
       <c r="A1" s="150" t="str" cm="1">
         <f t="array" ref="A1">INDEX(T,2,lang)</f>
         <v>2026 World Cup Final Tournament Schedule</v>
@@ -40101,7 +40101,7 @@
       <c r="AW1" s="125"/>
       <c r="AX1" s="125"/>
     </row>
-    <row r="2" spans="1:95" ht="3" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:95" ht="3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="S2" s="123"/>
       <c r="T2" s="123"/>
       <c r="AC2" s="123"/>
@@ -40117,7 +40117,7 @@
       <c r="AW2" s="125"/>
       <c r="AX2" s="125"/>
     </row>
-    <row r="3" spans="1:95" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:95" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="10"/>
       <c r="B3" s="10"/>
       <c r="C3" s="10"/>
@@ -40152,8 +40152,8 @@
       <c r="AW3" s="125"/>
       <c r="AX3" s="125"/>
     </row>
-    <row r="4" spans="1:95" ht="3" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="5" spans="1:95" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:95" ht="3" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="5" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A5" s="152" t="str" cm="1">
         <f t="array" ref="A5">INDEX(T,3,lang)</f>
         <v>Group Stage</v>
@@ -40175,7 +40175,7 @@
       <c r="O5" s="159"/>
       <c r="P5" s="160"/>
     </row>
-    <row r="6" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="155"/>
       <c r="B6" s="156"/>
       <c r="C6" s="156"/>
@@ -40332,7 +40332,7 @@
       <c r="CI6" s="145"/>
       <c r="CJ6" s="146"/>
     </row>
-    <row r="7" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="11">
         <v>1</v>
       </c>
@@ -40428,7 +40428,7 @@
       <c r="CI7" s="148"/>
       <c r="CJ7" s="149"/>
     </row>
-    <row r="8" spans="1:95" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A8" s="16">
         <v>2</v>
       </c>
@@ -40675,7 +40675,7 @@
       <c r="CP8" s="21"/>
       <c r="CQ8" s="21"/>
     </row>
-    <row r="9" spans="1:95" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A9" s="16">
         <v>3</v>
       </c>
@@ -40940,7 +40940,7 @@
       <c r="CP9" s="21"/>
       <c r="CQ9" s="21"/>
     </row>
-    <row r="10" spans="1:95" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A10" s="16">
         <v>4</v>
       </c>
@@ -41205,7 +41205,7 @@
       <c r="CP10" s="21"/>
       <c r="CQ10" s="21"/>
     </row>
-    <row r="11" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="16">
         <v>5</v>
       </c>
@@ -41430,7 +41430,7 @@
       <c r="BK11" s="142"/>
       <c r="BL11" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!G3,AK80:AS91,9,FALSE),"3rd Group A/B/C/D/F")</f>
-        <v>3rd Group A/B/C/D/F</v>
+        <v>Scotland</v>
       </c>
       <c r="BM11" s="62">
         <v>0</v>
@@ -41474,7 +41474,7 @@
       <c r="CP11" s="21"/>
       <c r="CQ11" s="21"/>
     </row>
-    <row r="12" spans="1:95" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A12" s="16">
         <v>6</v>
       </c>
@@ -41703,7 +41703,7 @@
       <c r="CP12" s="21"/>
       <c r="CQ12" s="21"/>
     </row>
-    <row r="13" spans="1:95" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A13" s="16">
         <v>7</v>
       </c>
@@ -41824,7 +41824,7 @@
       <c r="CP13" s="21"/>
       <c r="CQ13" s="21"/>
     </row>
-    <row r="14" spans="1:95" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A14" s="16">
         <v>8</v>
       </c>
@@ -42093,7 +42093,7 @@
       <c r="CP14" s="21"/>
       <c r="CQ14" s="21"/>
     </row>
-    <row r="15" spans="1:95" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A15" s="16">
         <v>9</v>
       </c>
@@ -42322,7 +42322,7 @@
       <c r="BK15" s="142"/>
       <c r="BL15" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!I3,AK80:AS91,9,FALSE),"3rd Group C/D/F/G/H")</f>
-        <v>3rd Group C/D/F/G/H</v>
+        <v>New Zealand</v>
       </c>
       <c r="BM15" s="62">
         <v>0</v>
@@ -42359,7 +42359,7 @@
       <c r="CH15" s="21"/>
       <c r="CI15" s="21"/>
     </row>
-    <row r="16" spans="1:95" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A16" s="16">
         <v>10</v>
       </c>
@@ -42617,7 +42617,7 @@
       <c r="CH16" s="21"/>
       <c r="CI16" s="21"/>
     </row>
-    <row r="17" spans="1:95" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A17" s="16">
         <v>11</v>
       </c>
@@ -42879,7 +42879,7 @@
       <c r="CH17" s="21"/>
       <c r="CI17" s="21"/>
     </row>
-    <row r="18" spans="1:95" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A18" s="16">
         <v>12</v>
       </c>
@@ -43101,7 +43101,7 @@
       <c r="CH18" s="21"/>
       <c r="CI18" s="21"/>
     </row>
-    <row r="19" spans="1:95" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A19" s="16">
         <v>13</v>
       </c>
@@ -43222,7 +43222,7 @@
       <c r="CP19" s="21"/>
       <c r="CQ19" s="21"/>
     </row>
-    <row r="20" spans="1:95" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A20" s="16">
         <v>14</v>
       </c>
@@ -43465,13 +43465,15 @@
       <c r="BT20" s="61">
         <v>1</v>
       </c>
-      <c r="BU20" s="63"/>
+      <c r="BU20" s="63">
+        <v>1</v>
+      </c>
       <c r="BV20" s="25">
         <v>5</v>
       </c>
       <c r="BW20" s="116">
         <f>IF(OR(BT20="",BT21="",AND(BU20="",BU21&lt;&gt;""),AND(BU21="",BU20&lt;&gt;""),AND(BV20="",BV21&lt;&gt;""),AND(BV21="",BV20&lt;&gt;"")),"",BT20*1000+BU20*10+BV20)</f>
-        <v>1005</v>
+        <v>1015</v>
       </c>
       <c r="BX20" s="112"/>
       <c r="BY20" s="21"/>
@@ -43493,7 +43495,7 @@
       <c r="CP20" s="21"/>
       <c r="CQ20" s="21"/>
     </row>
-    <row r="21" spans="1:95" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A21" s="16">
         <v>15</v>
       </c>
@@ -43740,13 +43742,15 @@
       <c r="BT21" s="62">
         <v>1</v>
       </c>
-      <c r="BU21" s="64"/>
+      <c r="BU21" s="64">
+        <v>1</v>
+      </c>
       <c r="BV21" s="27">
         <v>4</v>
       </c>
       <c r="BW21" s="112">
         <f>IF(BW20="","",BT21*1000+BU21*10+BV21)</f>
-        <v>1004</v>
+        <v>1014</v>
       </c>
       <c r="BX21" s="112"/>
       <c r="BY21" s="21"/>
@@ -43768,7 +43772,7 @@
       <c r="CP21" s="21"/>
       <c r="CQ21" s="21"/>
     </row>
-    <row r="22" spans="1:95" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A22" s="16">
         <v>16</v>
       </c>
@@ -43840,15 +43844,15 @@
       </c>
       <c r="U22" s="123">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" s="123">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W22" s="123">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X22" s="123">
         <f t="shared" si="9"/>
@@ -44034,7 +44038,7 @@
         <v>46217.791666666672</v>
       </c>
     </row>
-    <row r="23" spans="1:95" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A23" s="16">
         <v>17</v>
       </c>
@@ -44302,7 +44306,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="24" spans="1:95" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A24" s="16">
         <v>18</v>
       </c>
@@ -44523,7 +44527,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="25" spans="1:95" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A25" s="16">
         <v>19</v>
       </c>
@@ -44637,7 +44641,7 @@
       <c r="CP25" s="21"/>
       <c r="CQ25" s="21"/>
     </row>
-    <row r="26" spans="1:95" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A26" s="16">
         <v>20</v>
       </c>
@@ -44907,7 +44911,7 @@
       <c r="CP26" s="21"/>
       <c r="CQ26" s="21"/>
     </row>
-    <row r="27" spans="1:95" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A27" s="16">
         <v>21</v>
       </c>
@@ -45181,7 +45185,7 @@
       <c r="CP27" s="21"/>
       <c r="CQ27" s="21"/>
     </row>
-    <row r="28" spans="1:95" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A28" s="16">
         <v>22</v>
       </c>
@@ -45442,7 +45446,7 @@
       <c r="CK28" s="114"/>
       <c r="CL28" s="112"/>
     </row>
-    <row r="29" spans="1:95" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A29" s="16">
         <v>23</v>
       </c>
@@ -45707,7 +45711,7 @@
       <c r="CK29" s="114"/>
       <c r="CL29" s="112"/>
     </row>
-    <row r="30" spans="1:95" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A30" s="16">
         <v>24</v>
       </c>
@@ -45932,7 +45936,7 @@
       <c r="CK30" s="114"/>
       <c r="CL30" s="112"/>
     </row>
-    <row r="31" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="16">
         <v>25</v>
       </c>
@@ -46044,7 +46048,7 @@
       <c r="CK31" s="114"/>
       <c r="CL31" s="112"/>
     </row>
-    <row r="32" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="16">
         <v>26</v>
       </c>
@@ -46304,7 +46308,7 @@
       <c r="CK32" s="114"/>
       <c r="CL32" s="112"/>
     </row>
-    <row r="33" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A33" s="16">
         <v>27</v>
       </c>
@@ -46576,7 +46580,7 @@
       <c r="CP33" s="145"/>
       <c r="CQ33" s="146"/>
     </row>
-    <row r="34" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A34" s="16">
         <v>28</v>
       </c>
@@ -46837,7 +46841,7 @@
       <c r="CP34" s="148"/>
       <c r="CQ34" s="149"/>
     </row>
-    <row r="35" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A35" s="16">
         <v>29</v>
       </c>
@@ -47062,7 +47066,7 @@
       <c r="BK35" s="142"/>
       <c r="BL35" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!F3,AK80:AS91,9,FALSE),"3rd Group B/E/F/I/J")</f>
-        <v>3rd Group B/E/F/I/J</v>
+        <v>Bosnia and Herzegovina</v>
       </c>
       <c r="BM35" s="62">
         <v>0</v>
@@ -47097,7 +47101,7 @@
       <c r="CK35" s="114"/>
       <c r="CL35" s="112"/>
     </row>
-    <row r="36" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A36" s="16">
         <v>30</v>
       </c>
@@ -47329,7 +47333,7 @@
         <v>46222.791666666672</v>
       </c>
     </row>
-    <row r="37" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A37" s="16">
         <v>31</v>
       </c>
@@ -47419,7 +47423,7 @@
       <c r="BR37" s="142"/>
       <c r="BS37" s="26" t="str">
         <f>IF(BP38&gt;BP39,BL38,IF(BP38&lt;BP39,BL39,""))</f>
-        <v>1G</v>
+        <v>Belgium</v>
       </c>
       <c r="BT37" s="62">
         <v>0</v>
@@ -47462,7 +47466,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="38" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A38" s="16">
         <v>32</v>
       </c>
@@ -47693,7 +47697,7 @@
       </c>
       <c r="BL38" s="24" t="str">
         <f>AS44</f>
-        <v>1G</v>
+        <v>Belgium</v>
       </c>
       <c r="BM38" s="61">
         <v>2</v>
@@ -47735,7 +47739,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="39" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A39" s="16">
         <v>33</v>
       </c>
@@ -47964,7 +47968,7 @@
       <c r="BK39" s="142"/>
       <c r="BL39" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!H3,AK80:AS91,9,FALSE),"3rd Group A/E/H/I/J")</f>
-        <v>3rd Group A/E/H/I/J</v>
+        <v>Saudi Arabia</v>
       </c>
       <c r="BM39" s="62">
         <v>0</v>
@@ -47996,7 +48000,7 @@
       <c r="CP39" s="21"/>
       <c r="CQ39" s="21"/>
     </row>
-    <row r="40" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A40" s="16">
         <v>34</v>
       </c>
@@ -48221,7 +48225,7 @@
       <c r="CK40" s="114"/>
       <c r="CL40" s="112"/>
     </row>
-    <row r="41" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A41" s="16">
         <v>35</v>
       </c>
@@ -48465,7 +48469,7 @@
       <c r="CK41" s="114"/>
       <c r="CL41" s="112"/>
     </row>
-    <row r="42" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A42" s="16">
         <v>36</v>
       </c>
@@ -48676,7 +48680,7 @@
       <c r="BW42" s="112"/>
       <c r="CK42" s="114"/>
     </row>
-    <row r="43" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A43" s="16">
         <v>37</v>
       </c>
@@ -48779,7 +48783,7 @@
       </c>
       <c r="CK43" s="114"/>
     </row>
-    <row r="44" spans="1:96" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:96" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="16">
         <v>38</v>
       </c>
@@ -48891,7 +48895,7 @@
       </c>
       <c r="AF44" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE44 &amp; "_win")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG44" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE44 &amp; "_draw")</f>
@@ -48919,15 +48923,15 @@
       </c>
       <c r="AN44" s="123">
         <f>AF44*3+AG44</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AO44" s="123">
         <f>AN44/AN48*10+BA44</f>
-        <v>9.5694613583138164</v>
+        <v>9</v>
       </c>
       <c r="AP44" s="123">
         <f>AO44*10000000+BI44*100+AM44/AM48*10+AI44/AI48*1++IF(AQ44=0,ROW(),AQ44)/2000000</f>
-        <v>95694623.689774752</v>
+        <v>90000010.106636584</v>
       </c>
       <c r="AQ44" s="126">
         <f>VLOOKUP(AE44,db_fifarank,2,FALSE)</f>
@@ -48935,15 +48939,15 @@
       </c>
       <c r="AR44" s="125">
         <f>AP44/AP48</f>
-        <v>0.99999998955009228</v>
+        <v>0.9999999888888903</v>
       </c>
       <c r="AS44" s="125" t="str">
         <f>IF(SUM(AF44:AH47)=12,J45,"1G")</f>
-        <v>1G</v>
+        <v>Belgium</v>
       </c>
       <c r="AT44" s="126" cm="1">
         <f t="array" ref="AT44">SUMPRODUCT(($S$7:$S$78=AE44&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE44&amp;"_win")*($U$7:$U$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU44" s="126" cm="1">
         <f t="array" ref="AU44">SUMPRODUCT(($S$7:$S$78=AE44&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE44&amp;"_draw")*($U$7:$U$78))</f>
@@ -48951,27 +48955,27 @@
       </c>
       <c r="AV44" s="126" cm="1">
         <f t="array" ref="AV44">SUMPRODUCT(($E$7:$E$78=AE44)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE44)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW44" s="126" cm="1">
         <f t="array" ref="AW44">SUMPRODUCT(($E$7:$E$78=AE44)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE44)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX44" s="126">
         <f>AV44-AW44</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY44" s="126">
         <f>AX44-MIN(AX44:AX47)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ44" s="126">
         <f>AT44/AT48*1000+AU44/AU48*100+AY44/AY48*10+AV44/AV48</f>
-        <v>507.33333333333337</v>
+        <v>0</v>
       </c>
       <c r="BA44" s="126">
         <f>AZ44/AZ48</f>
-        <v>0.99803278688524588</v>
+        <v>0</v>
       </c>
       <c r="BB44" s="126" cm="1">
         <f t="array" ref="BB44">SUMPRODUCT(($S$7:$S$78=AE44&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE44&amp;"_win")*($X$7:$X$78))</f>
@@ -49038,7 +49042,7 @@
       <c r="CP44" s="145"/>
       <c r="CQ44" s="146"/>
     </row>
-    <row r="45" spans="1:96" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:96" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="16">
         <v>39</v>
       </c>
@@ -49061,7 +49065,9 @@
       <c r="F45" s="19">
         <v>3</v>
       </c>
-      <c r="G45" s="20"/>
+      <c r="G45" s="20">
+        <v>0</v>
+      </c>
       <c r="H45" s="80" t="str">
         <f>AE46</f>
         <v>Iran</v>
@@ -49072,11 +49078,11 @@
       </c>
       <c r="K45" s="31">
         <f>L45+M45+N45</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L45" s="31">
         <f>VLOOKUP(1,AD44:AN47,3,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M45" s="31">
         <f>VLOOKUP(1,AD44:AN47,4,FALSE)</f>
@@ -49092,7 +49098,7 @@
       </c>
       <c r="P45" s="32">
         <f>L45*3+M45</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="R45" s="123">
         <f>DATE(2026,6,21)+TIME(8,0,0)+gmt_delta</f>
@@ -49100,11 +49106,11 @@
       </c>
       <c r="S45" s="127" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Belgium_win</v>
       </c>
       <c r="T45" s="127" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Iran_lose</v>
       </c>
       <c r="U45" s="123">
         <f t="shared" si="8"/>
@@ -49134,9 +49140,9 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AB45" s="123" t="str">
+      <c r="AB45" s="123">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AD45" s="123">
         <f>COUNTIF(AR44:AR47,CONCATENATE("&gt;=",AR45))</f>
@@ -49180,11 +49186,11 @@
       </c>
       <c r="AO45" s="123">
         <f>AN45/AN48*10+BA45</f>
-        <v>8.5720843091334888</v>
+        <v>6</v>
       </c>
       <c r="AP45" s="123">
         <f>AO45*10000000+BI45*100+AM45/AM48*10+AI45/AI48*1++IF(AQ45=0,ROW(),AQ45)/2000000</f>
-        <v>85720850.640193447</v>
+        <v>60000007.548858538</v>
       </c>
       <c r="AQ45" s="126">
         <f>VLOOKUP(AE45,db_fifarank,2,FALSE)</f>
@@ -49192,11 +49198,11 @@
       </c>
       <c r="AR45" s="125">
         <f>AP45/AP48</f>
-        <v>0.89577498128118971</v>
+        <v>0.66666666827149035</v>
       </c>
       <c r="AS45" s="125" t="str">
         <f>IF(SUM(AF44:AH47)=12,J46,"2G")</f>
-        <v>2G</v>
+        <v>Egypt</v>
       </c>
       <c r="AT45" s="126" cm="1">
         <f t="array" ref="AT45">SUMPRODUCT(($S$7:$S$78=AE45&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE45&amp;"_win")*($U$7:$U$78))</f>
@@ -49208,15 +49214,15 @@
       </c>
       <c r="AV45" s="126" cm="1">
         <f t="array" ref="AV45">SUMPRODUCT(($E$7:$E$78=AE45)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE45)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW45" s="126" cm="1">
         <f t="array" ref="AW45">SUMPRODUCT(($E$7:$E$78=AE45)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE45)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX45" s="126">
         <f>AV45-AW45</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AY45" s="126">
         <f>AX45-MIN(AX44:AX47)</f>
@@ -49224,11 +49230,11 @@
       </c>
       <c r="AZ45" s="126">
         <f>AT45/AT48*1000+AU45/AU48*100+AY45/AY48*10+AV45/AV48</f>
-        <v>0.33333333333333331</v>
+        <v>0</v>
       </c>
       <c r="BA45" s="126">
         <f>AZ45/AZ48</f>
-        <v>6.5573770491803268E-4</v>
+        <v>0</v>
       </c>
       <c r="BB45" s="126" cm="1">
         <f t="array" ref="BB45">SUMPRODUCT(($S$7:$S$78=AE45&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE45&amp;"_win")*($X$7:$X$78))</f>
@@ -49296,7 +49302,7 @@
       <c r="CP45" s="148"/>
       <c r="CQ45" s="149"/>
     </row>
-    <row r="46" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A46" s="16">
         <v>40</v>
       </c>
@@ -49416,7 +49422,7 @@
       </c>
       <c r="AH46" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE46 &amp; "_lose")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI46" s="123">
         <f>SUMIF($E$7:$E$78,$AE46,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE46,$G$7:$G$78)</f>
@@ -49440,11 +49446,11 @@
       </c>
       <c r="AO46" s="123">
         <f>AN46/AN48*10+BA46</f>
-        <v>6.557377049180327E-3</v>
+        <v>0</v>
       </c>
       <c r="AP46" s="123">
         <f>AO46*10000000+BI46*100+AM46/AM48*10+AI46/AI48*1++IF(AQ46=0,ROW(),AQ46)/2000000</f>
-        <v>65573.771299453263</v>
+        <v>8.0764999999999993E-4</v>
       </c>
       <c r="AQ46" s="126">
         <f>VLOOKUP(AE46,db_fifarank,2,FALSE)</f>
@@ -49452,7 +49458,7 @@
       </c>
       <c r="AR46" s="125">
         <f>AP46/AP48</f>
-        <v>6.8523986077621358E-4</v>
+        <v>8.9738877814476614E-12</v>
       </c>
       <c r="AT46" s="126" cm="1">
         <f t="array" ref="AT46">SUMPRODUCT(($S$7:$S$78=AE46&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE46&amp;"_win")*($U$7:$U$78))</f>
@@ -49476,15 +49482,15 @@
       </c>
       <c r="AY46" s="126">
         <f>AX46-MIN(AX44:AX47)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ46" s="126">
         <f>AT46/AT48*1000+AU46/AU48*100+AY46/AY48*10+AV46/AV48</f>
-        <v>3.333333333333333</v>
+        <v>0</v>
       </c>
       <c r="BA46" s="126">
         <f>AZ46/AZ48</f>
-        <v>6.557377049180327E-3</v>
+        <v>0</v>
       </c>
       <c r="BB46" s="126" cm="1">
         <f t="array" ref="BB46">SUMPRODUCT(($S$7:$S$78=AE46&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE46&amp;"_win")*($X$7:$X$78))</f>
@@ -49544,7 +49550,7 @@
       <c r="CK46" s="114"/>
       <c r="CL46" s="112"/>
     </row>
-    <row r="47" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A47" s="16">
         <v>41</v>
       </c>
@@ -49688,11 +49694,11 @@
       </c>
       <c r="AO47" s="123">
         <f>AN47/AN48*10+BA47</f>
-        <v>4.2922716627634658</v>
+        <v>3</v>
       </c>
       <c r="AP47" s="123">
         <f>AO47*10000000+BI47*100+AM47/AM48*10+AI47/AI48*1++IF(AQ47=0,ROW(),AQ47)/2000000</f>
-        <v>42922719.060967751</v>
+        <v>30000002.433333091</v>
       </c>
       <c r="AQ47" s="126">
         <f>VLOOKUP(AE47,db_fifarank,2,FALSE)</f>
@@ -49700,7 +49706,7 @@
       </c>
       <c r="AR47" s="125">
         <f>AP47/AP48</f>
-        <v>0.44853845448598295</v>
+        <v>0.33333331923467835</v>
       </c>
       <c r="AT47" s="126" cm="1">
         <f t="array" ref="AT47">SUMPRODUCT(($S$7:$S$78=AE47&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE47&amp;"_win")*($U$7:$U$78))</f>
@@ -49724,15 +49730,15 @@
       </c>
       <c r="AY47" s="126">
         <f>AX47-MIN(AX44:AX47)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ47" s="126">
         <f>AT47/AT48*1000+AU47/AU48*100+AY47/AY48*10+AV47/AV48</f>
-        <v>3.333333333333333</v>
+        <v>0</v>
       </c>
       <c r="BA47" s="126">
         <f>AZ47/AZ48</f>
-        <v>6.557377049180327E-3</v>
+        <v>0</v>
       </c>
       <c r="BB47" s="126" cm="1">
         <f t="array" ref="BB47">SUMPRODUCT(($S$7:$S$78=AE47&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE47&amp;"_win")*($X$7:$X$78))</f>
@@ -49815,7 +49821,7 @@
         <v>46221.875</v>
       </c>
     </row>
-    <row r="48" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A48" s="16">
         <v>42</v>
       </c>
@@ -49851,7 +49857,7 @@
       </c>
       <c r="K48" s="36">
         <f>L48+M48+N48</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L48" s="36">
         <f>VLOOKUP(4,AD44:AN47,3,FALSE)</f>
@@ -49863,7 +49869,7 @@
       </c>
       <c r="N48" s="36">
         <f>VLOOKUP(4,AD44:AN47,5,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O48" s="36" t="str">
         <f>VLOOKUP(4,AD44:AN47,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD44:AN47,7,FALSE)</f>
@@ -49919,7 +49925,7 @@
       </c>
       <c r="AF48" s="123">
         <f t="shared" ref="AF48:AH48" si="24">MAX(AF44:AF47)-MIN(AF44:AF47)+1</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG48" s="123">
         <f t="shared" si="24"/>
@@ -49927,7 +49933,7 @@
       </c>
       <c r="AH48" s="123">
         <f t="shared" si="24"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI48" s="123">
         <f>MAX(AI44:AI47)+1</f>
@@ -49943,19 +49949,19 @@
       </c>
       <c r="AN48" s="123">
         <f>MAX(AN44:AN47)+1</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AO48" s="123">
         <f>MAX(AO44:AO47)+1</f>
-        <v>10.569461358313816</v>
+        <v>10</v>
       </c>
       <c r="AP48" s="123">
         <f>MAX(AP44:AP47)+1</f>
-        <v>95694624.689774752</v>
+        <v>90000011.106636584</v>
       </c>
       <c r="AT48" s="126">
         <f>MAX(AT44:AT47)-MIN(AT44:AT47)+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU48" s="126">
         <f>MAX(AU44:AU47)-MIN(AU44:AU47)+1</f>
@@ -49963,19 +49969,19 @@
       </c>
       <c r="AV48" s="126">
         <f>MAX(AV44:AV47)-MIN(AV44:AV47)+1</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AW48" s="126">
         <f>MAX(AW44:AW47)-MIN(AW44:AW47)+1</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AY48" s="126">
         <f>MAX(AY44:AY47)-MIN(AY44:AY47)+1</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AZ48" s="126">
         <f>MAX(AZ44:AZ47)+1</f>
-        <v>508.33333333333337</v>
+        <v>1</v>
       </c>
       <c r="BB48" s="126">
         <f>MAX(BB44:BB47)-MIN(BB44:BB47)+1</f>
@@ -50050,7 +50056,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="49" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A49" s="16">
         <v>43</v>
       </c>
@@ -50175,7 +50181,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="50" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A50" s="16">
         <v>44</v>
       </c>
@@ -50434,7 +50440,7 @@
       <c r="CK50" s="114"/>
       <c r="CL50" s="112"/>
     </row>
-    <row r="51" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A51" s="16">
         <v>45</v>
       </c>
@@ -50663,7 +50669,7 @@
       <c r="BK51" s="142"/>
       <c r="BL51" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!D3,AK80:AS91,9,FALSE),"3rd Group C/E/F/H/I")</f>
-        <v>3rd Group C/E/F/H/I</v>
+        <v>Ivory Coast</v>
       </c>
       <c r="BM51" s="62">
         <v>0</v>
@@ -50697,7 +50703,7 @@
       <c r="CK51" s="114"/>
       <c r="CL51" s="112"/>
     </row>
-    <row r="52" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A52" s="16">
         <v>46</v>
       </c>
@@ -50952,7 +50958,7 @@
       <c r="CK52" s="114"/>
       <c r="CL52" s="112"/>
     </row>
-    <row r="53" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A53" s="16">
         <v>47</v>
       </c>
@@ -51211,7 +51217,7 @@
       <c r="CK53" s="114"/>
       <c r="CL53" s="112"/>
     </row>
-    <row r="54" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A54" s="16">
         <v>48</v>
       </c>
@@ -51442,7 +51448,7 @@
       </c>
       <c r="CL54" s="112"/>
     </row>
-    <row r="55" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A55" s="16">
         <v>49</v>
       </c>
@@ -51527,7 +51533,7 @@
       <c r="BK55" s="142"/>
       <c r="BL55" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!K3,AK80:AS91,9,FALSE),"3rd Group E/H/I/J/K")</f>
-        <v>3rd Group E/H/I/J/K</v>
+        <v>Senegal</v>
       </c>
       <c r="BM55" s="62">
         <v>0</v>
@@ -51571,7 +51577,7 @@
       </c>
       <c r="CL55" s="112"/>
     </row>
-    <row r="56" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A56" s="16">
         <v>50</v>
       </c>
@@ -51834,7 +51840,7 @@
       </c>
       <c r="CL56" s="112"/>
     </row>
-    <row r="57" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A57" s="16">
         <v>51</v>
       </c>
@@ -52088,7 +52094,7 @@
       <c r="CC57" s="21"/>
       <c r="CD57" s="114"/>
     </row>
-    <row r="58" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A58" s="16">
         <v>52</v>
       </c>
@@ -52342,7 +52348,7 @@
       <c r="CC58" s="21"/>
       <c r="CD58" s="114"/>
     </row>
-    <row r="59" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A59" s="16">
         <v>53</v>
       </c>
@@ -52600,7 +52606,7 @@
       <c r="CC59" s="21"/>
       <c r="CD59" s="114"/>
     </row>
-    <row r="60" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A60" s="16">
         <v>54</v>
       </c>
@@ -52818,7 +52824,7 @@
       <c r="CC60" s="21"/>
       <c r="CD60" s="114"/>
     </row>
-    <row r="61" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A61" s="16">
         <v>55</v>
       </c>
@@ -52935,7 +52941,7 @@
       <c r="CC61" s="21"/>
       <c r="CD61" s="114"/>
     </row>
-    <row r="62" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A62" s="16">
         <v>56</v>
       </c>
@@ -53193,7 +53199,7 @@
       <c r="CC62" s="21"/>
       <c r="CD62" s="114"/>
     </row>
-    <row r="63" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A63" s="16">
         <v>57</v>
       </c>
@@ -53423,7 +53429,7 @@
       <c r="BK63" s="142"/>
       <c r="BL63" s="26" t="str">
         <f>AS45</f>
-        <v>2G</v>
+        <v>Egypt</v>
       </c>
       <c r="BM63" s="62">
         <v>1</v>
@@ -53455,7 +53461,7 @@
         <v>46215.041666666672</v>
       </c>
     </row>
-    <row r="64" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A64" s="16">
         <v>58</v>
       </c>
@@ -53709,7 +53715,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="65" spans="1:95" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A65" s="16">
         <v>59</v>
       </c>
@@ -53967,7 +53973,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="66" spans="1:95" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A66" s="16">
         <v>60</v>
       </c>
@@ -54178,7 +54184,7 @@
       <c r="BV66" s="21"/>
       <c r="BW66" s="114"/>
     </row>
-    <row r="67" spans="1:95" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A67" s="16">
         <v>61</v>
       </c>
@@ -54263,7 +54269,7 @@
       <c r="BK67" s="142"/>
       <c r="BL67" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!E3,AK80:AS91,9,FALSE),"3rd Group E/F/G/I/J")</f>
-        <v>3rd Group E/F/G/I/J</v>
+        <v>Algeria</v>
       </c>
       <c r="BM67" s="62">
         <v>0</v>
@@ -54288,7 +54294,7 @@
         <v>46210.833333333336</v>
       </c>
     </row>
-    <row r="68" spans="1:95" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A68" s="16">
         <v>62</v>
       </c>
@@ -54558,7 +54564,7 @@
       <c r="CP68" s="131"/>
       <c r="CQ68" s="131"/>
     </row>
-    <row r="69" spans="1:95" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A69" s="16">
         <v>63</v>
       </c>
@@ -54826,7 +54832,7 @@
       <c r="CP69" s="131"/>
       <c r="CQ69" s="131"/>
     </row>
-    <row r="70" spans="1:95" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A70" s="16">
         <v>64</v>
       </c>
@@ -55068,7 +55074,7 @@
       <c r="BQ70" s="112"/>
       <c r="BW70" s="112"/>
     </row>
-    <row r="71" spans="1:95" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A71" s="16">
         <v>65</v>
       </c>
@@ -55294,7 +55300,7 @@
       <c r="BK71" s="142"/>
       <c r="BL71" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!J3,AK80:AS91,9,FALSE),"3rd Group D/E/I/J/L")</f>
-        <v>3rd Group D/E/I/J/L</v>
+        <v>Ghana</v>
       </c>
       <c r="BM71" s="62">
         <v>0</v>
@@ -55307,7 +55313,7 @@
       </c>
       <c r="BQ71" s="112"/>
     </row>
-    <row r="72" spans="1:95" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A72" s="16">
         <v>66</v>
       </c>
@@ -55495,7 +55501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:95" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A73" s="16">
         <v>67</v>
       </c>
@@ -55578,7 +55584,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="74" spans="1:95" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A74" s="16">
         <v>68</v>
       </c>
@@ -55806,7 +55812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:95" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A75" s="16">
         <v>69</v>
       </c>
@@ -56034,7 +56040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:95" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A76" s="16">
         <v>70</v>
       </c>
@@ -56258,7 +56264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:95" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A77" s="16">
         <v>71</v>
       </c>
@@ -56482,7 +56488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:95" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A78" s="16">
         <v>72</v>
       </c>
@@ -56670,7 +56676,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:95" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A79" s="73"/>
       <c r="B79" s="73"/>
       <c r="C79" s="73"/>
@@ -56688,7 +56694,7 @@
       <c r="O79" s="70"/>
       <c r="P79" s="70"/>
     </row>
-    <row r="80" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:95" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="73"/>
       <c r="B80" s="73"/>
       <c r="C80" s="73"/>
@@ -56790,7 +56796,7 @@
         <v>Ⓐ South Africa</v>
       </c>
     </row>
-    <row r="81" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="73"/>
       <c r="B81" s="73"/>
       <c r="C81" s="73"/>
@@ -56892,7 +56898,7 @@
         <v>Ⓑ Bosnia and Herzegovina</v>
       </c>
     </row>
-    <row r="82" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="73"/>
       <c r="B82" s="73"/>
       <c r="C82" s="73"/>
@@ -56994,7 +57000,7 @@
         <v>Ⓒ Scotland</v>
       </c>
     </row>
-    <row r="83" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="73"/>
       <c r="B83" s="73"/>
       <c r="C83" s="132" t="s">
@@ -57098,7 +57104,7 @@
         <v>Ⓓ United States</v>
       </c>
     </row>
-    <row r="84" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="73"/>
       <c r="B84" s="73"/>
       <c r="C84" s="135"/>
@@ -57212,7 +57218,7 @@
         <v>Ⓔ Ivory Coast</v>
       </c>
     </row>
-    <row r="85" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="73"/>
       <c r="B85" s="73"/>
       <c r="C85" s="135"/>
@@ -57326,7 +57332,7 @@
         <v>Ⓕ Tunisia</v>
       </c>
     </row>
-    <row r="86" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="73"/>
       <c r="B86" s="73"/>
       <c r="C86" s="135"/>
@@ -57440,7 +57446,7 @@
         <v>Ⓖ New Zealand</v>
       </c>
     </row>
-    <row r="87" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="73"/>
       <c r="B87" s="73"/>
       <c r="C87" s="135"/>
@@ -57554,7 +57560,7 @@
         <v>Ⓗ Saudi Arabia</v>
       </c>
     </row>
-    <row r="88" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="73"/>
       <c r="B88" s="73"/>
       <c r="C88" s="138"/>
@@ -57668,7 +57674,7 @@
         <v>Ⓘ Senegal</v>
       </c>
     </row>
-    <row r="89" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="73"/>
       <c r="B89" s="73"/>
       <c r="C89" s="73"/>
@@ -57782,7 +57788,7 @@
         <v>Ⓙ Algeria</v>
       </c>
     </row>
-    <row r="90" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="73"/>
       <c r="B90" s="73"/>
       <c r="C90" s="73"/>
@@ -57896,7 +57902,7 @@
         <v>Ⓚ DR Congo</v>
       </c>
     </row>
-    <row r="91" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="73"/>
       <c r="B91" s="73"/>
       <c r="C91" s="73"/>
@@ -57940,11 +57946,11 @@
       </c>
       <c r="S91" s="127" t="str">
         <f>IF(OR(BM38="",BM39=""),"",IF(BM38&gt;BM39,BL38,IF(BM38&lt;BM39,BL39,IF(OR(BN38="",BN39=""),"draw",IF(BN38&gt;BN39,BL38,IF(BN38&lt;BN39,BL39,IF(OR(BO38="",BO39=""),"draw",IF(BO38&gt;BO39,BL38,IF(BO38&lt;BO39,BL39,"draw")))))))))</f>
-        <v>1G</v>
+        <v>Belgium</v>
       </c>
       <c r="T91" s="127" t="str" cm="1">
         <f t="array" ref="T91">IF(OR(S91="",S91="draw"),INDEX(T,93,lang),S91)</f>
-        <v>1G</v>
+        <v>Belgium</v>
       </c>
       <c r="AD91" s="123">
         <f t="shared" si="38"/>
@@ -58010,7 +58016,7 @@
         <v>Ⓛ Ghana</v>
       </c>
     </row>
-    <row r="92" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="73"/>
       <c r="B92" s="73"/>
       <c r="C92" s="73"/>
@@ -58082,10 +58088,10 @@
       </c>
       <c r="AS92" s="126" t="b">
         <f>SUM(K9:K78)=144</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:46" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A93" s="73"/>
       <c r="B93" s="73"/>
       <c r="C93" s="73"/>
@@ -58103,7 +58109,7 @@
       <c r="O93" s="70"/>
       <c r="P93" s="70"/>
     </row>
-    <row r="95" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:46" x14ac:dyDescent="0.35">
       <c r="R95" s="123">
         <f>DATE(2026,12,9)+TIME(8,0,0)+gmt_delta</f>
         <v>46365.791666666672</v>
@@ -58117,21 +58123,21 @@
         <v>France</v>
       </c>
     </row>
-    <row r="96" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="R96" s="123">
         <f>DATE(2026,12,9)+TIME(4,0,0)+gmt_delta</f>
         <v>46365.625</v>
       </c>
       <c r="S96" s="127" t="str">
         <f>IF(OR(BT20="",BT21=""),"",IF(BT20&gt;BT21,BS20,IF(BT20&lt;BT21,BS21,IF(OR(BU20="",BU21=""),"draw",IF(BU20&gt;BU21,BS20,IF(BU20&lt;BU21,BS21,IF(OR(BV20="",BV21=""),"draw",IF(BV20&gt;BV21,BS20,IF(BV20&lt;BV21,BS21,"draw")))))))))</f>
-        <v>draw</v>
-      </c>
-      <c r="T96" s="127" cm="1">
+        <v>Mexico</v>
+      </c>
+      <c r="T96" s="127" t="str" cm="1">
         <f t="array" ref="T96">IF(OR(S96="",S96="draw"),INDEX(T,95,lang),S96)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="18:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>Mexico</v>
+      </c>
+    </row>
+    <row r="97" spans="18:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="R97" s="123">
         <f>DATE(2026,12,10)+TIME(8,0,0)+gmt_delta</f>
         <v>46366.791666666672</v>
@@ -58145,7 +58151,7 @@
         <v>Spain</v>
       </c>
     </row>
-    <row r="98" spans="18:29" x14ac:dyDescent="0.3">
+    <row r="98" spans="18:29" x14ac:dyDescent="0.35">
       <c r="R98" s="123">
         <f>DATE(2026,12,10)+TIME(4,0,0)+gmt_delta</f>
         <v>46366.625</v>
@@ -58159,7 +58165,7 @@
         <v>Turkey</v>
       </c>
     </row>
-    <row r="102" spans="18:29" x14ac:dyDescent="0.3">
+    <row r="102" spans="18:29" x14ac:dyDescent="0.35">
       <c r="R102" s="123">
         <f>DATE(2026,12,13)+TIME(8,0,0)+gmt_delta</f>
         <v>46369.791666666672</v>
@@ -58185,7 +58191,7 @@
         <v>Mexico</v>
       </c>
     </row>
-    <row r="103" spans="18:29" x14ac:dyDescent="0.3">
+    <row r="103" spans="18:29" x14ac:dyDescent="0.35">
       <c r="R103" s="123">
         <f>DATE(2026,12,14)+TIME(8,0,0)+gmt_delta</f>
         <v>46370.791666666672</v>
@@ -58211,7 +58217,7 @@
         <v>Turkey</v>
       </c>
     </row>
-    <row r="107" spans="18:29" x14ac:dyDescent="0.3">
+    <row r="107" spans="18:29" x14ac:dyDescent="0.35">
       <c r="R107" s="123">
         <f>DATE(2026,12,17)+TIME(8,0,0)+gmt_delta</f>
         <v>46373.791666666672</v>
@@ -58221,7 +58227,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="111" spans="18:29" x14ac:dyDescent="0.3">
+    <row r="111" spans="18:29" x14ac:dyDescent="0.35">
       <c r="R111" s="123">
         <f>DATE(2026,12,18)+TIME(8,0,0)+gmt_delta</f>
         <v>46374.791666666672</v>
@@ -59307,22 +59313,22 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47A2A316-429C-49FB-9962-F944380EA825}">
   <dimension ref="B1:K500"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="2.44140625" style="82" customWidth="1"/>
-    <col min="2" max="2" width="9.21875" style="81"/>
-    <col min="3" max="3" width="13.77734375" style="81" customWidth="1"/>
-    <col min="4" max="11" width="9.44140625" style="81" customWidth="1"/>
-    <col min="12" max="16384" width="9.21875" style="82"/>
+    <col min="1" max="1" width="2.453125" style="82" customWidth="1"/>
+    <col min="2" max="2" width="9.1796875" style="81"/>
+    <col min="3" max="3" width="13.81640625" style="81" customWidth="1"/>
+    <col min="4" max="11" width="9.453125" style="81" customWidth="1"/>
+    <col min="12" max="16384" width="9.1796875" style="82"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="8.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:11" ht="21" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:11" ht="8.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:11" ht="21" x14ac:dyDescent="0.35">
       <c r="B2" s="108" t="s">
         <v>3193</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B3" s="109">
         <f>MATCH(C3,C6:C500,0)</f>
         <v>93</v>
@@ -59364,7 +59370,7 @@
         <v>3I</v>
       </c>
     </row>
-    <row r="5" spans="2:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="84" t="s">
         <v>3194</v>
       </c>
@@ -59394,7 +59400,7 @@
         <v>3202</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B6" s="88">
         <v>1</v>
       </c>
@@ -59426,7 +59432,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B7" s="88">
         <v>2</v>
       </c>
@@ -59458,7 +59464,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B8" s="88">
         <v>3</v>
       </c>
@@ -59490,7 +59496,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B9" s="88">
         <v>4</v>
       </c>
@@ -59522,7 +59528,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B10" s="88">
         <v>5</v>
       </c>
@@ -59554,7 +59560,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B11" s="88">
         <v>6</v>
       </c>
@@ -59586,7 +59592,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B12" s="88">
         <v>7</v>
       </c>
@@ -59618,7 +59624,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B13" s="88">
         <v>8</v>
       </c>
@@ -59650,7 +59656,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B14" s="88">
         <v>9</v>
       </c>
@@ -59682,7 +59688,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B15" s="88">
         <v>10</v>
       </c>
@@ -59714,7 +59720,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B16" s="88">
         <v>11</v>
       </c>
@@ -59746,7 +59752,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B17" s="88">
         <v>12</v>
       </c>
@@ -59778,7 +59784,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B18" s="88">
         <v>13</v>
       </c>
@@ -59810,7 +59816,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B19" s="88">
         <v>14</v>
       </c>
@@ -59842,7 +59848,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B20" s="88">
         <v>15</v>
       </c>
@@ -59874,7 +59880,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B21" s="88">
         <v>16</v>
       </c>
@@ -59906,7 +59912,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B22" s="88">
         <v>17</v>
       </c>
@@ -59938,7 +59944,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B23" s="88">
         <v>18</v>
       </c>
@@ -59970,7 +59976,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B24" s="88">
         <v>19</v>
       </c>
@@ -60002,7 +60008,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B25" s="88">
         <v>20</v>
       </c>
@@ -60034,7 +60040,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B26" s="88">
         <v>21</v>
       </c>
@@ -60066,7 +60072,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B27" s="88">
         <v>22</v>
       </c>
@@ -60098,7 +60104,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B28" s="88">
         <v>23</v>
       </c>
@@ -60130,7 +60136,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B29" s="88">
         <v>24</v>
       </c>
@@ -60162,7 +60168,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B30" s="88">
         <v>25</v>
       </c>
@@ -60194,7 +60200,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B31" s="88">
         <v>26</v>
       </c>
@@ -60226,7 +60232,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B32" s="88">
         <v>27</v>
       </c>
@@ -60258,7 +60264,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B33" s="88">
         <v>28</v>
       </c>
@@ -60290,7 +60296,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B34" s="88">
         <v>29</v>
       </c>
@@ -60322,7 +60328,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B35" s="88">
         <v>30</v>
       </c>
@@ -60354,7 +60360,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B36" s="88">
         <v>31</v>
       </c>
@@ -60386,7 +60392,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B37" s="88">
         <v>32</v>
       </c>
@@ -60418,7 +60424,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B38" s="88">
         <v>33</v>
       </c>
@@ -60450,7 +60456,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B39" s="88">
         <v>34</v>
       </c>
@@ -60482,7 +60488,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B40" s="88">
         <v>35</v>
       </c>
@@ -60514,7 +60520,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B41" s="88">
         <v>36</v>
       </c>
@@ -60546,7 +60552,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B42" s="88">
         <v>37</v>
       </c>
@@ -60578,7 +60584,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B43" s="88">
         <v>38</v>
       </c>
@@ -60610,7 +60616,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B44" s="88">
         <v>39</v>
       </c>
@@ -60642,7 +60648,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B45" s="88">
         <v>40</v>
       </c>
@@ -60674,7 +60680,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B46" s="88">
         <v>41</v>
       </c>
@@ -60706,7 +60712,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B47" s="88">
         <v>42</v>
       </c>
@@ -60738,7 +60744,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B48" s="88">
         <v>43</v>
       </c>
@@ -60770,7 +60776,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="49" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B49" s="88">
         <v>44</v>
       </c>
@@ -60802,7 +60808,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="50" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B50" s="88">
         <v>45</v>
       </c>
@@ -60834,7 +60840,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="51" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B51" s="88">
         <v>46</v>
       </c>
@@ -60866,7 +60872,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="52" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B52" s="88">
         <v>47</v>
       </c>
@@ -60898,7 +60904,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="53" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B53" s="88">
         <v>48</v>
       </c>
@@ -60930,7 +60936,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B54" s="88">
         <v>49</v>
       </c>
@@ -60962,7 +60968,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="55" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B55" s="88">
         <v>50</v>
       </c>
@@ -60994,7 +61000,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="56" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B56" s="88">
         <v>51</v>
       </c>
@@ -61026,7 +61032,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="57" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B57" s="88">
         <v>52</v>
       </c>
@@ -61058,7 +61064,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="58" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B58" s="88">
         <v>53</v>
       </c>
@@ -61090,7 +61096,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="59" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B59" s="88">
         <v>54</v>
       </c>
@@ -61122,7 +61128,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="60" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B60" s="88">
         <v>55</v>
       </c>
@@ -61154,7 +61160,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="61" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B61" s="88">
         <v>56</v>
       </c>
@@ -61186,7 +61192,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="62" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B62" s="88">
         <v>57</v>
       </c>
@@ -61218,7 +61224,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="63" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B63" s="88">
         <v>58</v>
       </c>
@@ -61250,7 +61256,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="64" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B64" s="88">
         <v>59</v>
       </c>
@@ -61282,7 +61288,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B65" s="88">
         <v>60</v>
       </c>
@@ -61314,7 +61320,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B66" s="88">
         <v>61</v>
       </c>
@@ -61346,7 +61352,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B67" s="88">
         <v>62</v>
       </c>
@@ -61378,7 +61384,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B68" s="88">
         <v>63</v>
       </c>
@@ -61410,7 +61416,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B69" s="88">
         <v>64</v>
       </c>
@@ -61442,7 +61448,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B70" s="88">
         <v>65</v>
       </c>
@@ -61474,7 +61480,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B71" s="88">
         <v>66</v>
       </c>
@@ -61506,7 +61512,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B72" s="88">
         <v>67</v>
       </c>
@@ -61538,7 +61544,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B73" s="88">
         <v>68</v>
       </c>
@@ -61570,7 +61576,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B74" s="88">
         <v>69</v>
       </c>
@@ -61602,7 +61608,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B75" s="88">
         <v>70</v>
       </c>
@@ -61634,7 +61640,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B76" s="88">
         <v>71</v>
       </c>
@@ -61666,7 +61672,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B77" s="88">
         <v>72</v>
       </c>
@@ -61698,7 +61704,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="78" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B78" s="88">
         <v>73</v>
       </c>
@@ -61730,7 +61736,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B79" s="88">
         <v>74</v>
       </c>
@@ -61762,7 +61768,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B80" s="88">
         <v>75</v>
       </c>
@@ -61794,7 +61800,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="81" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B81" s="88">
         <v>76</v>
       </c>
@@ -61826,7 +61832,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="82" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B82" s="88">
         <v>77</v>
       </c>
@@ -61858,7 +61864,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="83" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B83" s="88">
         <v>78</v>
       </c>
@@ -61890,7 +61896,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="84" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B84" s="88">
         <v>79</v>
       </c>
@@ -61922,7 +61928,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="85" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B85" s="88">
         <v>80</v>
       </c>
@@ -61954,7 +61960,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="86" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B86" s="88">
         <v>81</v>
       </c>
@@ -61986,7 +61992,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="87" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B87" s="88">
         <v>82</v>
       </c>
@@ -62018,7 +62024,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="88" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B88" s="88">
         <v>83</v>
       </c>
@@ -62050,7 +62056,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="89" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B89" s="88">
         <v>84</v>
       </c>
@@ -62082,7 +62088,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="90" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B90" s="88">
         <v>85</v>
       </c>
@@ -62114,7 +62120,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="91" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B91" s="88">
         <v>86</v>
       </c>
@@ -62146,7 +62152,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="92" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B92" s="88">
         <v>87</v>
       </c>
@@ -62178,7 +62184,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="93" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B93" s="88">
         <v>88</v>
       </c>
@@ -62210,7 +62216,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="94" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B94" s="88">
         <v>89</v>
       </c>
@@ -62242,7 +62248,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="95" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B95" s="88">
         <v>90</v>
       </c>
@@ -62274,7 +62280,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="96" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B96" s="88">
         <v>91</v>
       </c>
@@ -62306,7 +62312,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="97" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B97" s="88">
         <v>92</v>
       </c>
@@ -62338,7 +62344,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="98" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B98" s="88">
         <v>93</v>
       </c>
@@ -62370,7 +62376,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="99" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B99" s="88">
         <v>94</v>
       </c>
@@ -62402,7 +62408,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="100" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B100" s="88">
         <v>95</v>
       </c>
@@ -62434,7 +62440,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="101" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B101" s="88">
         <v>96</v>
       </c>
@@ -62466,7 +62472,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="102" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B102" s="88">
         <v>97</v>
       </c>
@@ -62498,7 +62504,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="103" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B103" s="88">
         <v>98</v>
       </c>
@@ -62530,7 +62536,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="104" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B104" s="88">
         <v>99</v>
       </c>
@@ -62562,7 +62568,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="105" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B105" s="88">
         <v>100</v>
       </c>
@@ -62594,7 +62600,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="106" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B106" s="88">
         <v>101</v>
       </c>
@@ -62626,7 +62632,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="107" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B107" s="88">
         <v>102</v>
       </c>
@@ -62658,7 +62664,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="108" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B108" s="88">
         <v>103</v>
       </c>
@@ -62690,7 +62696,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="109" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B109" s="88">
         <v>104</v>
       </c>
@@ -62722,7 +62728,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="110" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B110" s="88">
         <v>105</v>
       </c>
@@ -62754,7 +62760,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="111" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B111" s="88">
         <v>106</v>
       </c>
@@ -62786,7 +62792,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="112" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="112" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B112" s="88">
         <v>107</v>
       </c>
@@ -62818,7 +62824,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="113" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="113" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B113" s="88">
         <v>108</v>
       </c>
@@ -62850,7 +62856,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="114" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="114" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B114" s="88">
         <v>109</v>
       </c>
@@ -62882,7 +62888,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="115" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="115" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B115" s="88">
         <v>110</v>
       </c>
@@ -62914,7 +62920,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="116" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B116" s="88">
         <v>111</v>
       </c>
@@ -62946,7 +62952,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="117" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B117" s="88">
         <v>112</v>
       </c>
@@ -62978,7 +62984,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="118" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="118" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B118" s="88">
         <v>113</v>
       </c>
@@ -63010,7 +63016,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="119" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="119" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B119" s="88">
         <v>114</v>
       </c>
@@ -63042,7 +63048,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="120" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="120" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B120" s="88">
         <v>115</v>
       </c>
@@ -63074,7 +63080,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="121" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="121" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B121" s="88">
         <v>116</v>
       </c>
@@ -63106,7 +63112,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="122" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="122" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B122" s="88">
         <v>117</v>
       </c>
@@ -63138,7 +63144,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="123" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="123" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B123" s="88">
         <v>118</v>
       </c>
@@ -63170,7 +63176,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="124" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="124" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B124" s="88">
         <v>119</v>
       </c>
@@ -63202,7 +63208,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="125" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="125" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B125" s="88">
         <v>120</v>
       </c>
@@ -63234,7 +63240,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="126" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="126" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B126" s="88">
         <v>121</v>
       </c>
@@ -63266,7 +63272,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="127" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="127" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B127" s="88">
         <v>122</v>
       </c>
@@ -63298,7 +63304,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="128" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="128" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B128" s="88">
         <v>123</v>
       </c>
@@ -63330,7 +63336,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="129" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="129" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B129" s="88">
         <v>124</v>
       </c>
@@ -63362,7 +63368,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="130" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="130" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B130" s="88">
         <v>125</v>
       </c>
@@ -63394,7 +63400,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="131" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="131" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B131" s="88">
         <v>126</v>
       </c>
@@ -63426,7 +63432,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="132" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="132" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B132" s="88">
         <v>127</v>
       </c>
@@ -63458,7 +63464,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="133" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="133" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B133" s="88">
         <v>128</v>
       </c>
@@ -63490,7 +63496,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="134" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="134" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B134" s="88">
         <v>129</v>
       </c>
@@ -63522,7 +63528,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="135" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="135" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B135" s="88">
         <v>130</v>
       </c>
@@ -63554,7 +63560,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="136" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="136" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B136" s="88">
         <v>131</v>
       </c>
@@ -63586,7 +63592,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="137" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="137" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B137" s="88">
         <v>132</v>
       </c>
@@ -63618,7 +63624,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="138" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="138" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B138" s="88">
         <v>133</v>
       </c>
@@ -63650,7 +63656,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="139" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="139" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B139" s="88">
         <v>134</v>
       </c>
@@ -63682,7 +63688,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="140" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="140" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B140" s="88">
         <v>135</v>
       </c>
@@ -63714,7 +63720,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="141" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="141" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B141" s="88">
         <v>136</v>
       </c>
@@ -63746,7 +63752,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="142" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="142" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B142" s="88">
         <v>137</v>
       </c>
@@ -63778,7 +63784,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="143" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="143" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B143" s="88">
         <v>138</v>
       </c>
@@ -63810,7 +63816,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="144" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="144" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B144" s="88">
         <v>139</v>
       </c>
@@ -63842,7 +63848,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="145" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="145" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B145" s="88">
         <v>140</v>
       </c>
@@ -63874,7 +63880,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="146" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="146" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B146" s="88">
         <v>141</v>
       </c>
@@ -63906,7 +63912,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="147" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="147" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B147" s="88">
         <v>142</v>
       </c>
@@ -63938,7 +63944,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="148" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="148" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B148" s="88">
         <v>143</v>
       </c>
@@ -63970,7 +63976,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="149" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="149" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B149" s="88">
         <v>144</v>
       </c>
@@ -64002,7 +64008,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="150" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="150" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B150" s="88">
         <v>145</v>
       </c>
@@ -64034,7 +64040,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="151" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="151" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B151" s="88">
         <v>146</v>
       </c>
@@ -64066,7 +64072,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="152" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="152" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B152" s="88">
         <v>147</v>
       </c>
@@ -64098,7 +64104,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="153" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="153" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B153" s="88">
         <v>148</v>
       </c>
@@ -64130,7 +64136,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="154" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="154" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B154" s="88">
         <v>149</v>
       </c>
@@ -64162,7 +64168,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="155" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="155" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B155" s="88">
         <v>150</v>
       </c>
@@ -64194,7 +64200,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="156" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="156" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B156" s="88">
         <v>151</v>
       </c>
@@ -64226,7 +64232,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="157" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="157" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B157" s="88">
         <v>152</v>
       </c>
@@ -64258,7 +64264,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="158" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="158" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B158" s="88">
         <v>153</v>
       </c>
@@ -64290,7 +64296,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="159" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="159" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B159" s="88">
         <v>154</v>
       </c>
@@ -64322,7 +64328,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="160" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="160" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B160" s="88">
         <v>155</v>
       </c>
@@ -64354,7 +64360,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="161" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="161" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B161" s="88">
         <v>156</v>
       </c>
@@ -64386,7 +64392,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="162" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="162" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B162" s="88">
         <v>157</v>
       </c>
@@ -64418,7 +64424,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="163" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="163" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B163" s="88">
         <v>158</v>
       </c>
@@ -64450,7 +64456,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="164" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="164" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B164" s="88">
         <v>159</v>
       </c>
@@ -64482,7 +64488,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="165" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="165" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B165" s="88">
         <v>160</v>
       </c>
@@ -64514,7 +64520,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="166" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="166" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B166" s="88">
         <v>161</v>
       </c>
@@ -64546,7 +64552,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="167" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="167" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B167" s="88">
         <v>162</v>
       </c>
@@ -64578,7 +64584,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="168" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="168" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B168" s="88">
         <v>163</v>
       </c>
@@ -64610,7 +64616,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="169" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="169" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B169" s="88">
         <v>164</v>
       </c>
@@ -64642,7 +64648,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="170" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="170" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B170" s="88">
         <v>165</v>
       </c>
@@ -64674,7 +64680,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="171" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="171" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B171" s="88">
         <v>166</v>
       </c>
@@ -64706,7 +64712,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="172" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="172" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B172" s="88">
         <v>167</v>
       </c>
@@ -64738,7 +64744,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="173" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="173" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B173" s="88">
         <v>168</v>
       </c>
@@ -64770,7 +64776,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="174" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="174" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B174" s="88">
         <v>169</v>
       </c>
@@ -64802,7 +64808,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="175" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="175" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B175" s="88">
         <v>170</v>
       </c>
@@ -64834,7 +64840,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="176" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="176" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B176" s="88">
         <v>171</v>
       </c>
@@ -64866,7 +64872,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="177" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="177" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B177" s="88">
         <v>172</v>
       </c>
@@ -64898,7 +64904,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="178" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="178" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B178" s="88">
         <v>173</v>
       </c>
@@ -64930,7 +64936,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="179" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="179" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B179" s="88">
         <v>174</v>
       </c>
@@ -64962,7 +64968,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="180" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="180" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B180" s="88">
         <v>175</v>
       </c>
@@ -64994,7 +65000,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="181" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="181" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B181" s="88">
         <v>176</v>
       </c>
@@ -65026,7 +65032,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="182" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="182" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B182" s="88">
         <v>177</v>
       </c>
@@ -65058,7 +65064,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="183" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="183" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B183" s="88">
         <v>178</v>
       </c>
@@ -65090,7 +65096,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="184" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="184" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B184" s="88">
         <v>179</v>
       </c>
@@ -65122,7 +65128,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="185" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="185" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B185" s="88">
         <v>180</v>
       </c>
@@ -65154,7 +65160,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="186" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="186" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B186" s="88">
         <v>181</v>
       </c>
@@ -65186,7 +65192,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="187" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="187" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B187" s="88">
         <v>182</v>
       </c>
@@ -65218,7 +65224,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="188" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="188" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B188" s="88">
         <v>183</v>
       </c>
@@ -65250,7 +65256,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="189" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="189" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B189" s="88">
         <v>184</v>
       </c>
@@ -65282,7 +65288,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="190" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="190" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B190" s="88">
         <v>185</v>
       </c>
@@ -65314,7 +65320,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="191" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="191" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B191" s="88">
         <v>186</v>
       </c>
@@ -65346,7 +65352,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="192" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="192" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B192" s="88">
         <v>187</v>
       </c>
@@ -65378,7 +65384,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="193" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B193" s="88">
         <v>188</v>
       </c>
@@ -65410,7 +65416,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="194" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B194" s="88">
         <v>189</v>
       </c>
@@ -65442,7 +65448,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="195" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B195" s="88">
         <v>190</v>
       </c>
@@ -65474,7 +65480,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="196" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B196" s="88">
         <v>191</v>
       </c>
@@ -65506,7 +65512,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="197" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B197" s="88">
         <v>192</v>
       </c>
@@ -65538,7 +65544,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="198" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B198" s="88">
         <v>193</v>
       </c>
@@ -65570,7 +65576,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="199" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B199" s="88">
         <v>194</v>
       </c>
@@ -65602,7 +65608,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="200" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="200" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B200" s="88">
         <v>195</v>
       </c>
@@ -65634,7 +65640,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="201" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="201" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B201" s="88">
         <v>196</v>
       </c>
@@ -65666,7 +65672,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="202" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="202" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B202" s="88">
         <v>197</v>
       </c>
@@ -65698,7 +65704,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="203" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="203" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B203" s="88">
         <v>198</v>
       </c>
@@ -65730,7 +65736,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="204" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="204" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B204" s="88">
         <v>199</v>
       </c>
@@ -65762,7 +65768,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="205" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="205" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B205" s="88">
         <v>200</v>
       </c>
@@ -65794,7 +65800,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="206" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="206" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B206" s="88">
         <v>201</v>
       </c>
@@ -65826,7 +65832,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="207" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="207" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B207" s="88">
         <v>202</v>
       </c>
@@ -65858,7 +65864,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="208" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="208" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B208" s="88">
         <v>203</v>
       </c>
@@ -65890,7 +65896,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="209" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="209" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B209" s="88">
         <v>204</v>
       </c>
@@ -65922,7 +65928,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="210" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="210" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B210" s="88">
         <v>205</v>
       </c>
@@ -65954,7 +65960,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="211" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="211" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B211" s="88">
         <v>206</v>
       </c>
@@ -65986,7 +65992,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="212" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="212" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B212" s="88">
         <v>207</v>
       </c>
@@ -66018,7 +66024,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="213" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="213" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B213" s="88">
         <v>208</v>
       </c>
@@ -66050,7 +66056,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="214" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="214" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B214" s="88">
         <v>209</v>
       </c>
@@ -66082,7 +66088,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="215" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="215" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B215" s="88">
         <v>210</v>
       </c>
@@ -66114,7 +66120,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="216" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="216" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B216" s="88">
         <v>211</v>
       </c>
@@ -66146,7 +66152,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="217" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="217" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B217" s="88">
         <v>212</v>
       </c>
@@ -66178,7 +66184,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="218" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="218" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B218" s="88">
         <v>213</v>
       </c>
@@ -66210,7 +66216,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="219" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="219" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B219" s="88">
         <v>214</v>
       </c>
@@ -66242,7 +66248,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="220" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="220" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B220" s="88">
         <v>215</v>
       </c>
@@ -66274,7 +66280,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="221" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="221" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B221" s="88">
         <v>216</v>
       </c>
@@ -66306,7 +66312,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="222" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="222" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B222" s="88">
         <v>217</v>
       </c>
@@ -66338,7 +66344,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="223" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="223" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B223" s="88">
         <v>218</v>
       </c>
@@ -66370,7 +66376,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="224" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="224" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B224" s="88">
         <v>219</v>
       </c>
@@ -66402,7 +66408,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="225" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="225" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B225" s="88">
         <v>220</v>
       </c>
@@ -66434,7 +66440,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="226" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="226" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B226" s="88">
         <v>221</v>
       </c>
@@ -66466,7 +66472,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="227" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="227" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B227" s="88">
         <v>222</v>
       </c>
@@ -66498,7 +66504,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="228" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="228" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B228" s="88">
         <v>223</v>
       </c>
@@ -66530,7 +66536,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="229" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="229" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B229" s="88">
         <v>224</v>
       </c>
@@ -66562,7 +66568,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="230" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="230" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B230" s="88">
         <v>225</v>
       </c>
@@ -66594,7 +66600,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="231" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="231" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B231" s="88">
         <v>226</v>
       </c>
@@ -66626,7 +66632,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="232" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="232" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B232" s="88">
         <v>227</v>
       </c>
@@ -66658,7 +66664,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="233" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="233" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B233" s="88">
         <v>228</v>
       </c>
@@ -66690,7 +66696,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="234" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="234" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B234" s="88">
         <v>229</v>
       </c>
@@ -66722,7 +66728,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="235" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="235" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B235" s="88">
         <v>230</v>
       </c>
@@ -66754,7 +66760,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="236" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="236" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B236" s="88">
         <v>231</v>
       </c>
@@ -66786,7 +66792,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="237" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="237" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B237" s="88">
         <v>232</v>
       </c>
@@ -66818,7 +66824,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="238" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="238" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B238" s="88">
         <v>233</v>
       </c>
@@ -66850,7 +66856,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="239" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="239" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B239" s="88">
         <v>234</v>
       </c>
@@ -66882,7 +66888,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="240" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="240" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B240" s="88">
         <v>235</v>
       </c>
@@ -66914,7 +66920,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="241" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="241" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B241" s="88">
         <v>236</v>
       </c>
@@ -66946,7 +66952,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="242" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="242" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B242" s="88">
         <v>237</v>
       </c>
@@ -66978,7 +66984,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="243" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="243" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B243" s="88">
         <v>238</v>
       </c>
@@ -67010,7 +67016,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="244" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="244" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B244" s="88">
         <v>239</v>
       </c>
@@ -67042,7 +67048,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="245" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="245" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B245" s="88">
         <v>240</v>
       </c>
@@ -67074,7 +67080,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="246" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="246" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B246" s="88">
         <v>241</v>
       </c>
@@ -67106,7 +67112,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="247" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="247" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B247" s="88">
         <v>242</v>
       </c>
@@ -67138,7 +67144,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="248" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="248" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B248" s="88">
         <v>243</v>
       </c>
@@ -67170,7 +67176,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="249" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="249" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B249" s="88">
         <v>244</v>
       </c>
@@ -67202,7 +67208,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="250" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="250" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B250" s="88">
         <v>245</v>
       </c>
@@ -67234,7 +67240,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="251" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="251" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B251" s="88">
         <v>246</v>
       </c>
@@ -67266,7 +67272,7 @@
         <v>3188</v>
       </c>
     </row>
-    <row r="252" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="252" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B252" s="88">
         <v>247</v>
       </c>
@@ -67298,7 +67304,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="253" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="253" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B253" s="88">
         <v>248</v>
       </c>
@@ -67330,7 +67336,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="254" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="254" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B254" s="88">
         <v>249</v>
       </c>
@@ -67362,7 +67368,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="255" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="255" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B255" s="88">
         <v>250</v>
       </c>
@@ -67394,7 +67400,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="256" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="256" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B256" s="88">
         <v>251</v>
       </c>
@@ -67426,7 +67432,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="257" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="257" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B257" s="88">
         <v>252</v>
       </c>
@@ -67458,7 +67464,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="258" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="258" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B258" s="88">
         <v>253</v>
       </c>
@@ -67490,7 +67496,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="259" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="259" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B259" s="88">
         <v>254</v>
       </c>
@@ -67522,7 +67528,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="260" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="260" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B260" s="88">
         <v>255</v>
       </c>
@@ -67554,7 +67560,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="261" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="261" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B261" s="88">
         <v>256</v>
       </c>
@@ -67586,7 +67592,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="262" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="262" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B262" s="88">
         <v>257</v>
       </c>
@@ -67618,7 +67624,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="263" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="263" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B263" s="88">
         <v>258</v>
       </c>
@@ -67650,7 +67656,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="264" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="264" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B264" s="88">
         <v>259</v>
       </c>
@@ -67682,7 +67688,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="265" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="265" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B265" s="88">
         <v>260</v>
       </c>
@@ -67714,7 +67720,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="266" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="266" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B266" s="88">
         <v>261</v>
       </c>
@@ -67746,7 +67752,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="267" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="267" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B267" s="88">
         <v>262</v>
       </c>
@@ -67778,7 +67784,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="268" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="268" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B268" s="88">
         <v>263</v>
       </c>
@@ -67810,7 +67816,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="269" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="269" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B269" s="88">
         <v>264</v>
       </c>
@@ -67842,7 +67848,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="270" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="270" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B270" s="88">
         <v>265</v>
       </c>
@@ -67874,7 +67880,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="271" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="271" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B271" s="88">
         <v>266</v>
       </c>
@@ -67906,7 +67912,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="272" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="272" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B272" s="88">
         <v>267</v>
       </c>
@@ -67938,7 +67944,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="273" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="273" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B273" s="88">
         <v>268</v>
       </c>
@@ -67970,7 +67976,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="274" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="274" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B274" s="88">
         <v>269</v>
       </c>
@@ -68002,7 +68008,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="275" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="275" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B275" s="88">
         <v>270</v>
       </c>
@@ -68034,7 +68040,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="276" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="276" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B276" s="88">
         <v>271</v>
       </c>
@@ -68066,7 +68072,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="277" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="277" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B277" s="88">
         <v>272</v>
       </c>
@@ -68098,7 +68104,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="278" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="278" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B278" s="88">
         <v>273</v>
       </c>
@@ -68130,7 +68136,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="279" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="279" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B279" s="88">
         <v>274</v>
       </c>
@@ -68162,7 +68168,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="280" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="280" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B280" s="88">
         <v>275</v>
       </c>
@@ -68194,7 +68200,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="281" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="281" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B281" s="88">
         <v>276</v>
       </c>
@@ -68226,7 +68232,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="282" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="282" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B282" s="88">
         <v>277</v>
       </c>
@@ -68258,7 +68264,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="283" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="283" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B283" s="88">
         <v>278</v>
       </c>
@@ -68290,7 +68296,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="284" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="284" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B284" s="88">
         <v>279</v>
       </c>
@@ -68322,7 +68328,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="285" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="285" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B285" s="88">
         <v>280</v>
       </c>
@@ -68354,7 +68360,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="286" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="286" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B286" s="88">
         <v>281</v>
       </c>
@@ -68386,7 +68392,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="287" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="287" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B287" s="88">
         <v>282</v>
       </c>
@@ -68418,7 +68424,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="288" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="288" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B288" s="88">
         <v>283</v>
       </c>
@@ -68450,7 +68456,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="289" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="289" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B289" s="88">
         <v>284</v>
       </c>
@@ -68482,7 +68488,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="290" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="290" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B290" s="88">
         <v>285</v>
       </c>
@@ -68514,7 +68520,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="291" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="291" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B291" s="88">
         <v>286</v>
       </c>
@@ -68546,7 +68552,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="292" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="292" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B292" s="88">
         <v>287</v>
       </c>
@@ -68578,7 +68584,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="293" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="293" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B293" s="88">
         <v>288</v>
       </c>
@@ -68610,7 +68616,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="294" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="294" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B294" s="88">
         <v>289</v>
       </c>
@@ -68642,7 +68648,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="295" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="295" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B295" s="88">
         <v>290</v>
       </c>
@@ -68674,7 +68680,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="296" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="296" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B296" s="88">
         <v>291</v>
       </c>
@@ -68706,7 +68712,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="297" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="297" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B297" s="88">
         <v>292</v>
       </c>
@@ -68738,7 +68744,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="298" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="298" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B298" s="88">
         <v>293</v>
       </c>
@@ -68770,7 +68776,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="299" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="299" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B299" s="88">
         <v>294</v>
       </c>
@@ -68802,7 +68808,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="300" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="300" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B300" s="88">
         <v>295</v>
       </c>
@@ -68834,7 +68840,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="301" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="301" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B301" s="88">
         <v>296</v>
       </c>
@@ -68866,7 +68872,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="302" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="302" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B302" s="88">
         <v>297</v>
       </c>
@@ -68898,7 +68904,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="303" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="303" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B303" s="88">
         <v>298</v>
       </c>
@@ -68930,7 +68936,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="304" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="304" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B304" s="88">
         <v>299</v>
       </c>
@@ -68962,7 +68968,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="305" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="305" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B305" s="88">
         <v>300</v>
       </c>
@@ -68994,7 +69000,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="306" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="306" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B306" s="88">
         <v>301</v>
       </c>
@@ -69026,7 +69032,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="307" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="307" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B307" s="88">
         <v>302</v>
       </c>
@@ -69058,7 +69064,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="308" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="308" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B308" s="88">
         <v>303</v>
       </c>
@@ -69090,7 +69096,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="309" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="309" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B309" s="88">
         <v>304</v>
       </c>
@@ -69122,7 +69128,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="310" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="310" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B310" s="88">
         <v>305</v>
       </c>
@@ -69154,7 +69160,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="311" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="311" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B311" s="88">
         <v>306</v>
       </c>
@@ -69186,7 +69192,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="312" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="312" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B312" s="88">
         <v>307</v>
       </c>
@@ -69218,7 +69224,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="313" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="313" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B313" s="88">
         <v>308</v>
       </c>
@@ -69250,7 +69256,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="314" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="314" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B314" s="88">
         <v>309</v>
       </c>
@@ -69282,7 +69288,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="315" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="315" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B315" s="88">
         <v>310</v>
       </c>
@@ -69314,7 +69320,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="316" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="316" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B316" s="88">
         <v>311</v>
       </c>
@@ -69346,7 +69352,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="317" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="317" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B317" s="88">
         <v>312</v>
       </c>
@@ -69378,7 +69384,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="318" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="318" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B318" s="88">
         <v>313</v>
       </c>
@@ -69410,7 +69416,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="319" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="319" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B319" s="88">
         <v>314</v>
       </c>
@@ -69442,7 +69448,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="320" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="320" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B320" s="88">
         <v>315</v>
       </c>
@@ -69474,7 +69480,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="321" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="321" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B321" s="88">
         <v>316</v>
       </c>
@@ -69506,7 +69512,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="322" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="322" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B322" s="88">
         <v>317</v>
       </c>
@@ -69538,7 +69544,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="323" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="323" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B323" s="88">
         <v>318</v>
       </c>
@@ -69570,7 +69576,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="324" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="324" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B324" s="88">
         <v>319</v>
       </c>
@@ -69602,7 +69608,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="325" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="325" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B325" s="88">
         <v>320</v>
       </c>
@@ -69634,7 +69640,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="326" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="326" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B326" s="88">
         <v>321</v>
       </c>
@@ -69666,7 +69672,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="327" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="327" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B327" s="88">
         <v>322</v>
       </c>
@@ -69698,7 +69704,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="328" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="328" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B328" s="88">
         <v>323</v>
       </c>
@@ -69730,7 +69736,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="329" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="329" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B329" s="88">
         <v>324</v>
       </c>
@@ -69762,7 +69768,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="330" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="330" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B330" s="88">
         <v>325</v>
       </c>
@@ -69794,7 +69800,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="331" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="331" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B331" s="88">
         <v>326</v>
       </c>
@@ -69826,7 +69832,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="332" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="332" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B332" s="88">
         <v>327</v>
       </c>
@@ -69858,7 +69864,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="333" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="333" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B333" s="88">
         <v>328</v>
       </c>
@@ -69890,7 +69896,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="334" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="334" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B334" s="88">
         <v>329</v>
       </c>
@@ -69922,7 +69928,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="335" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="335" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B335" s="88">
         <v>330</v>
       </c>
@@ -69954,7 +69960,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="336" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="336" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B336" s="88">
         <v>331</v>
       </c>
@@ -69986,7 +69992,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="337" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="337" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B337" s="88">
         <v>332</v>
       </c>
@@ -70018,7 +70024,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="338" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="338" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B338" s="88">
         <v>333</v>
       </c>
@@ -70050,7 +70056,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="339" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="339" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B339" s="88">
         <v>334</v>
       </c>
@@ -70082,7 +70088,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="340" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="340" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B340" s="88">
         <v>335</v>
       </c>
@@ -70114,7 +70120,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="341" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="341" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B341" s="88">
         <v>336</v>
       </c>
@@ -70146,7 +70152,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="342" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="342" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B342" s="88">
         <v>337</v>
       </c>
@@ -70178,7 +70184,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="343" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="343" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B343" s="88">
         <v>338</v>
       </c>
@@ -70210,7 +70216,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="344" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="344" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B344" s="88">
         <v>339</v>
       </c>
@@ -70242,7 +70248,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="345" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="345" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B345" s="88">
         <v>340</v>
       </c>
@@ -70274,7 +70280,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="346" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="346" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B346" s="88">
         <v>341</v>
       </c>
@@ -70306,7 +70312,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="347" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="347" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B347" s="88">
         <v>342</v>
       </c>
@@ -70338,7 +70344,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="348" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="348" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B348" s="88">
         <v>343</v>
       </c>
@@ -70370,7 +70376,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="349" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="349" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B349" s="88">
         <v>344</v>
       </c>
@@ -70402,7 +70408,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="350" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="350" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B350" s="88">
         <v>345</v>
       </c>
@@ -70434,7 +70440,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="351" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="351" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B351" s="88">
         <v>346</v>
       </c>
@@ -70466,7 +70472,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="352" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="352" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B352" s="88">
         <v>347</v>
       </c>
@@ -70498,7 +70504,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="353" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="353" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B353" s="88">
         <v>348</v>
       </c>
@@ -70530,7 +70536,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="354" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="354" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B354" s="88">
         <v>349</v>
       </c>
@@ -70562,7 +70568,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="355" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="355" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B355" s="88">
         <v>350</v>
       </c>
@@ -70594,7 +70600,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="356" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="356" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B356" s="88">
         <v>351</v>
       </c>
@@ -70626,7 +70632,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="357" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="357" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B357" s="88">
         <v>352</v>
       </c>
@@ -70658,7 +70664,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="358" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="358" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B358" s="88">
         <v>353</v>
       </c>
@@ -70690,7 +70696,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="359" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="359" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B359" s="88">
         <v>354</v>
       </c>
@@ -70722,7 +70728,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="360" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="360" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B360" s="88">
         <v>355</v>
       </c>
@@ -70754,7 +70760,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="361" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="361" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B361" s="88">
         <v>356</v>
       </c>
@@ -70786,7 +70792,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="362" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="362" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B362" s="88">
         <v>357</v>
       </c>
@@ -70818,7 +70824,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="363" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="363" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B363" s="88">
         <v>358</v>
       </c>
@@ -70850,7 +70856,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="364" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="364" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B364" s="88">
         <v>359</v>
       </c>
@@ -70882,7 +70888,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="365" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="365" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B365" s="88">
         <v>360</v>
       </c>
@@ -70914,7 +70920,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="366" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="366" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B366" s="88">
         <v>361</v>
       </c>
@@ -70946,7 +70952,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="367" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="367" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B367" s="88">
         <v>362</v>
       </c>
@@ -70978,7 +70984,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="368" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="368" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B368" s="88">
         <v>363</v>
       </c>
@@ -71010,7 +71016,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="369" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="369" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B369" s="88">
         <v>364</v>
       </c>
@@ -71042,7 +71048,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="370" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="370" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B370" s="88">
         <v>365</v>
       </c>
@@ -71074,7 +71080,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="371" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="371" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B371" s="88">
         <v>366</v>
       </c>
@@ -71106,7 +71112,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="372" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="372" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B372" s="88">
         <v>367</v>
       </c>
@@ -71138,7 +71144,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="373" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="373" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B373" s="88">
         <v>368</v>
       </c>
@@ -71170,7 +71176,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="374" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="374" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B374" s="88">
         <v>369</v>
       </c>
@@ -71202,7 +71208,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="375" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="375" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B375" s="88">
         <v>370</v>
       </c>
@@ -71234,7 +71240,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="376" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="376" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B376" s="88">
         <v>371</v>
       </c>
@@ -71266,7 +71272,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="377" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="377" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B377" s="88">
         <v>372</v>
       </c>
@@ -71298,7 +71304,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="378" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="378" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B378" s="88">
         <v>373</v>
       </c>
@@ -71330,7 +71336,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="379" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="379" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B379" s="88">
         <v>374</v>
       </c>
@@ -71362,7 +71368,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="380" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="380" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B380" s="88">
         <v>375</v>
       </c>
@@ -71394,7 +71400,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="381" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="381" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B381" s="88">
         <v>376</v>
       </c>
@@ -71426,7 +71432,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="382" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="382" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B382" s="88">
         <v>377</v>
       </c>
@@ -71458,7 +71464,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="383" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="383" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B383" s="88">
         <v>378</v>
       </c>
@@ -71490,7 +71496,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="384" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="384" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B384" s="88">
         <v>379</v>
       </c>
@@ -71522,7 +71528,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="385" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="385" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B385" s="88">
         <v>380</v>
       </c>
@@ -71554,7 +71560,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="386" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="386" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B386" s="88">
         <v>381</v>
       </c>
@@ -71586,7 +71592,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="387" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="387" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B387" s="88">
         <v>382</v>
       </c>
@@ -71618,7 +71624,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="388" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="388" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B388" s="88">
         <v>383</v>
       </c>
@@ -71650,7 +71656,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="389" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="389" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B389" s="88">
         <v>384</v>
       </c>
@@ -71682,7 +71688,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="390" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="390" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B390" s="88">
         <v>385</v>
       </c>
@@ -71714,7 +71720,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="391" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="391" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B391" s="88">
         <v>386</v>
       </c>
@@ -71746,7 +71752,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="392" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="392" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B392" s="88">
         <v>387</v>
       </c>
@@ -71778,7 +71784,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="393" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="393" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B393" s="88">
         <v>388</v>
       </c>
@@ -71810,7 +71816,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="394" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="394" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B394" s="88">
         <v>389</v>
       </c>
@@ -71842,7 +71848,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="395" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="395" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B395" s="88">
         <v>390</v>
       </c>
@@ -71874,7 +71880,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="396" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="396" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B396" s="88">
         <v>391</v>
       </c>
@@ -71906,7 +71912,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="397" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="397" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B397" s="88">
         <v>392</v>
       </c>
@@ -71938,7 +71944,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="398" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="398" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B398" s="88">
         <v>393</v>
       </c>
@@ -71970,7 +71976,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="399" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="399" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B399" s="88">
         <v>394</v>
       </c>
@@ -72002,7 +72008,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="400" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="400" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B400" s="88">
         <v>395</v>
       </c>
@@ -72034,7 +72040,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="401" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="401" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B401" s="88">
         <v>396</v>
       </c>
@@ -72066,7 +72072,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="402" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="402" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B402" s="88">
         <v>397</v>
       </c>
@@ -72098,7 +72104,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="403" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="403" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B403" s="88">
         <v>398</v>
       </c>
@@ -72130,7 +72136,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="404" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="404" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B404" s="88">
         <v>399</v>
       </c>
@@ -72162,7 +72168,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="405" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="405" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B405" s="88">
         <v>400</v>
       </c>
@@ -72194,7 +72200,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="406" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="406" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B406" s="88">
         <v>401</v>
       </c>
@@ -72226,7 +72232,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="407" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="407" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B407" s="88">
         <v>402</v>
       </c>
@@ -72258,7 +72264,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="408" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="408" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B408" s="88">
         <v>403</v>
       </c>
@@ -72290,7 +72296,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="409" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="409" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B409" s="88">
         <v>404</v>
       </c>
@@ -72322,7 +72328,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="410" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="410" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B410" s="88">
         <v>405</v>
       </c>
@@ -72354,7 +72360,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="411" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="411" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B411" s="88">
         <v>406</v>
       </c>
@@ -72386,7 +72392,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="412" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="412" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B412" s="88">
         <v>407</v>
       </c>
@@ -72418,7 +72424,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="413" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="413" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B413" s="88">
         <v>408</v>
       </c>
@@ -72450,7 +72456,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="414" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="414" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B414" s="88">
         <v>409</v>
       </c>
@@ -72482,7 +72488,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="415" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="415" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B415" s="88">
         <v>410</v>
       </c>
@@ -72514,7 +72520,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="416" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="416" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B416" s="88">
         <v>411</v>
       </c>
@@ -72546,7 +72552,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="417" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="417" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B417" s="88">
         <v>412</v>
       </c>
@@ -72578,7 +72584,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="418" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="418" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B418" s="88">
         <v>413</v>
       </c>
@@ -72610,7 +72616,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="419" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="419" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B419" s="88">
         <v>414</v>
       </c>
@@ -72642,7 +72648,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="420" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="420" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B420" s="88">
         <v>415</v>
       </c>
@@ -72674,7 +72680,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="421" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="421" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B421" s="88">
         <v>416</v>
       </c>
@@ -72706,7 +72712,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="422" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="422" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B422" s="88">
         <v>417</v>
       </c>
@@ -72738,7 +72744,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="423" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="423" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B423" s="88">
         <v>418</v>
       </c>
@@ -72770,7 +72776,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="424" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="424" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B424" s="88">
         <v>419</v>
       </c>
@@ -72802,7 +72808,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="425" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="425" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B425" s="88">
         <v>420</v>
       </c>
@@ -72834,7 +72840,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="426" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="426" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B426" s="88">
         <v>421</v>
       </c>
@@ -72866,7 +72872,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="427" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="427" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B427" s="88">
         <v>422</v>
       </c>
@@ -72898,7 +72904,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="428" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="428" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B428" s="88">
         <v>423</v>
       </c>
@@ -72930,7 +72936,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="429" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="429" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B429" s="88">
         <v>424</v>
       </c>
@@ -72962,7 +72968,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="430" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="430" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B430" s="88">
         <v>425</v>
       </c>
@@ -72994,7 +73000,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="431" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="431" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B431" s="88">
         <v>426</v>
       </c>
@@ -73026,7 +73032,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="432" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="432" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B432" s="88">
         <v>427</v>
       </c>
@@ -73058,7 +73064,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="433" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="433" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B433" s="88">
         <v>428</v>
       </c>
@@ -73090,7 +73096,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="434" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="434" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B434" s="88">
         <v>429</v>
       </c>
@@ -73122,7 +73128,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="435" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="435" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B435" s="88">
         <v>430</v>
       </c>
@@ -73154,7 +73160,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="436" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="436" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B436" s="88">
         <v>431</v>
       </c>
@@ -73186,7 +73192,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="437" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="437" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B437" s="88">
         <v>432</v>
       </c>
@@ -73218,7 +73224,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="438" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="438" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B438" s="88">
         <v>433</v>
       </c>
@@ -73250,7 +73256,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="439" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="439" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B439" s="88">
         <v>434</v>
       </c>
@@ -73282,7 +73288,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="440" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="440" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B440" s="88">
         <v>435</v>
       </c>
@@ -73314,7 +73320,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="441" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="441" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B441" s="88">
         <v>436</v>
       </c>
@@ -73346,7 +73352,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="442" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="442" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B442" s="88">
         <v>437</v>
       </c>
@@ -73378,7 +73384,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="443" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="443" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B443" s="88">
         <v>438</v>
       </c>
@@ -73410,7 +73416,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="444" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="444" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B444" s="88">
         <v>439</v>
       </c>
@@ -73442,7 +73448,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="445" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="445" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B445" s="88">
         <v>440</v>
       </c>
@@ -73474,7 +73480,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="446" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="446" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B446" s="88">
         <v>441</v>
       </c>
@@ -73506,7 +73512,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="447" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="447" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B447" s="88">
         <v>442</v>
       </c>
@@ -73538,7 +73544,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="448" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="448" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B448" s="88">
         <v>443</v>
       </c>
@@ -73570,7 +73576,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="449" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="449" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B449" s="88">
         <v>444</v>
       </c>
@@ -73602,7 +73608,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="450" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="450" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B450" s="88">
         <v>445</v>
       </c>
@@ -73634,7 +73640,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="451" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="451" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B451" s="88">
         <v>446</v>
       </c>
@@ -73666,7 +73672,7 @@
         <v>3188</v>
       </c>
     </row>
-    <row r="452" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="452" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B452" s="88">
         <v>447</v>
       </c>
@@ -73698,7 +73704,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="453" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="453" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B453" s="88">
         <v>448</v>
       </c>
@@ -73730,7 +73736,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="454" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="454" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B454" s="88">
         <v>449</v>
       </c>
@@ -73762,7 +73768,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="455" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="455" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B455" s="88">
         <v>450</v>
       </c>
@@ -73794,7 +73800,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="456" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="456" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B456" s="88">
         <v>451</v>
       </c>
@@ -73826,7 +73832,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="457" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="457" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B457" s="88">
         <v>452</v>
       </c>
@@ -73858,7 +73864,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="458" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="458" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B458" s="88">
         <v>453</v>
       </c>
@@ -73890,7 +73896,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="459" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="459" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B459" s="88">
         <v>454</v>
       </c>
@@ -73922,7 +73928,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="460" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="460" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B460" s="88">
         <v>455</v>
       </c>
@@ -73954,7 +73960,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="461" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="461" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B461" s="88">
         <v>456</v>
       </c>
@@ -73986,7 +73992,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="462" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="462" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B462" s="88">
         <v>457</v>
       </c>
@@ -74018,7 +74024,7 @@
         <v>3188</v>
       </c>
     </row>
-    <row r="463" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="463" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B463" s="88">
         <v>458</v>
       </c>
@@ -74050,7 +74056,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="464" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="464" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B464" s="88">
         <v>459</v>
       </c>
@@ -74082,7 +74088,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="465" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="465" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B465" s="88">
         <v>460</v>
       </c>
@@ -74114,7 +74120,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="466" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="466" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B466" s="88">
         <v>461</v>
       </c>
@@ -74146,7 +74152,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="467" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="467" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B467" s="88">
         <v>462</v>
       </c>
@@ -74178,7 +74184,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="468" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="468" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B468" s="88">
         <v>463</v>
       </c>
@@ -74210,7 +74216,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="469" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="469" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B469" s="88">
         <v>464</v>
       </c>
@@ -74242,7 +74248,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="470" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="470" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B470" s="88">
         <v>465</v>
       </c>
@@ -74274,7 +74280,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="471" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="471" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B471" s="88">
         <v>466</v>
       </c>
@@ -74306,7 +74312,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="472" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="472" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B472" s="88">
         <v>467</v>
       </c>
@@ -74338,7 +74344,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="473" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="473" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B473" s="88">
         <v>468</v>
       </c>
@@ -74370,7 +74376,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="474" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="474" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B474" s="88">
         <v>469</v>
       </c>
@@ -74402,7 +74408,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="475" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="475" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B475" s="88">
         <v>470</v>
       </c>
@@ -74434,7 +74440,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="476" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="476" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B476" s="88">
         <v>471</v>
       </c>
@@ -74466,7 +74472,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="477" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="477" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B477" s="88">
         <v>472</v>
       </c>
@@ -74498,7 +74504,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="478" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="478" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B478" s="88">
         <v>473</v>
       </c>
@@ -74530,7 +74536,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="479" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="479" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B479" s="88">
         <v>474</v>
       </c>
@@ -74562,7 +74568,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="480" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="480" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B480" s="88">
         <v>475</v>
       </c>
@@ -74594,7 +74600,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="481" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="481" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B481" s="88">
         <v>476</v>
       </c>
@@ -74626,7 +74632,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="482" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="482" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B482" s="88">
         <v>477</v>
       </c>
@@ -74658,7 +74664,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="483" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="483" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B483" s="88">
         <v>478</v>
       </c>
@@ -74690,7 +74696,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="484" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="484" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B484" s="88">
         <v>479</v>
       </c>
@@ -74722,7 +74728,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="485" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="485" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B485" s="88">
         <v>480</v>
       </c>
@@ -74754,7 +74760,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="486" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="486" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B486" s="88">
         <v>481</v>
       </c>
@@ -74786,7 +74792,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="487" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="487" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B487" s="88">
         <v>482</v>
       </c>
@@ -74818,7 +74824,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="488" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="488" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B488" s="88">
         <v>483</v>
       </c>
@@ -74850,7 +74856,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="489" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="489" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B489" s="88">
         <v>484</v>
       </c>
@@ -74882,7 +74888,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="490" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="490" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B490" s="88">
         <v>485</v>
       </c>
@@ -74914,7 +74920,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="491" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="491" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B491" s="88">
         <v>486</v>
       </c>
@@ -74946,7 +74952,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="492" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="492" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B492" s="88">
         <v>487</v>
       </c>
@@ -74978,7 +74984,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="493" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="493" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B493" s="88">
         <v>488</v>
       </c>
@@ -75010,7 +75016,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="494" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="494" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B494" s="88">
         <v>489</v>
       </c>
@@ -75042,7 +75048,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="495" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="495" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B495" s="88">
         <v>490</v>
       </c>
@@ -75074,7 +75080,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="496" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="496" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B496" s="88">
         <v>491</v>
       </c>
@@ -75106,7 +75112,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="497" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="497" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B497" s="88">
         <v>492</v>
       </c>
@@ -75138,7 +75144,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="498" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="498" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B498" s="88">
         <v>493</v>
       </c>
@@ -75170,7 +75176,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="499" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="499" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B499" s="88">
         <v>494</v>
       </c>
@@ -75202,7 +75208,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="500" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="500" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B500" s="90">
         <v>495</v>
       </c>
